--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Hiopos Lleida.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Hiopos Lleida.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2140.64</v>
+        <v>2449.28</v>
       </c>
       <c r="C2" t="n">
-        <v>2149.66</v>
+        <v>2461.320000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>108.389233646251</v>
+        <v>108.6002632733655</v>
       </c>
       <c r="E2" t="n">
-        <v>116.250942009434</v>
+        <v>116.4009555848081</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5166093928980527</v>
+        <v>0.5198609731876862</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1590864246250987</v>
+        <v>0.155931131614498</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2943548387096774</v>
+        <v>0.291958041958042</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3012600229095074</v>
+        <v>0.2874875868917577</v>
       </c>
       <c r="J2" t="n">
-        <v>301</v>
+        <v>343</v>
       </c>
       <c r="K2" t="n">
-        <v>287</v>
+        <v>327</v>
       </c>
       <c r="L2" t="n">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="M2" t="n">
-        <v>360</v>
+        <v>407</v>
       </c>
       <c r="N2" t="n">
-        <v>904</v>
+        <v>1038</v>
       </c>
       <c r="O2" t="n">
-        <v>1200</v>
+        <v>1386</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6872852233676976</v>
+        <v>0.6881827209533267</v>
       </c>
       <c r="Q2" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="R2" t="n">
-        <v>292</v>
+        <v>323</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1672394043528064</v>
+        <v>0.160377358490566</v>
       </c>
       <c r="T2" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="U2" t="n">
-        <v>252</v>
+        <v>296</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1443298969072165</v>
+        <v>0.1469712015888779</v>
       </c>
       <c r="W2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="X2" t="n">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09335624284077892</v>
+        <v>0.09235352532274081</v>
       </c>
       <c r="Z2" t="n">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="AA2" t="n">
-        <v>520</v>
+        <v>585</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.297823596792669</v>
+        <v>0.2904667328699106</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7533333333333333</v>
+        <v>0.7489177489177489</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.3835616438356164</v>
+        <v>0.3777089783281734</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3134920634920635</v>
+        <v>0.3277027027027027</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3987730061349693</v>
+        <v>0.3763440860215054</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3019230769230769</v>
+        <v>0.3008547008547008</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.506666666666667</v>
+        <v>1.497835497835498</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.626984126984127</v>
+        <v>0.6554054054054054</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.9751098096632503</v>
+        <v>0.9571984435797666</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.8931750741839762</v>
+        <v>0.8886010362694301</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.9828767123287672</v>
+        <v>0.9790419161676647</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.606382978723404</v>
+        <v>1.614678899082569</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.217054263565891</v>
+        <v>1.258064516129032</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.511627906976744</v>
+        <v>4.640552995391705</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.728682170542636</v>
+        <v>5.898617511520738</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>76.45142857142858</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>76.77357142857144</v>
+        <v>76.91625000000002</v>
       </c>
       <c r="D3" t="n">
-        <v>108.389233646251</v>
+        <v>108.6002632733655</v>
       </c>
       <c r="E3" t="n">
-        <v>116.250942009434</v>
+        <v>116.4009555848081</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5166093928980526</v>
+        <v>0.5198609731876862</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1590864246250986</v>
+        <v>0.155931131614498</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2943548387096774</v>
+        <v>0.291958041958042</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3012600229095074</v>
+        <v>0.2874875868917577</v>
       </c>
       <c r="J3" t="n">
-        <v>10.75</v>
+        <v>10.71875</v>
       </c>
       <c r="K3" t="n">
-        <v>10.25</v>
+        <v>10.21875</v>
       </c>
       <c r="L3" t="n">
-        <v>5.392857142857143</v>
+        <v>5.5</v>
       </c>
       <c r="M3" t="n">
-        <v>12.85714285714286</v>
+        <v>12.71875</v>
       </c>
       <c r="N3" t="n">
-        <v>32.28571428571428</v>
+        <v>32.4375</v>
       </c>
       <c r="O3" t="n">
-        <v>42.85714285714285</v>
+        <v>43.3125</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6872852233676975</v>
+        <v>0.6881827209533267</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>3.8125</v>
       </c>
       <c r="R3" t="n">
-        <v>10.42857142857143</v>
+        <v>10.09375</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1672394043528064</v>
+        <v>0.160377358490566</v>
       </c>
       <c r="T3" t="n">
-        <v>2.821428571428572</v>
+        <v>3.03125</v>
       </c>
       <c r="U3" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1443298969072165</v>
+        <v>0.1469712015888779</v>
       </c>
       <c r="W3" t="n">
-        <v>2.321428571428572</v>
+        <v>2.1875</v>
       </c>
       <c r="X3" t="n">
-        <v>5.821428571428571</v>
+        <v>5.8125</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.09335624284077891</v>
+        <v>0.09235352532274081</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.607142857142857</v>
+        <v>5.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.57142857142857</v>
+        <v>18.28125</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.297823596792669</v>
+        <v>0.2904667328699106</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7533333333333334</v>
+        <v>0.7489177489177489</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.3835616438356164</v>
+        <v>0.3777089783281734</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3134920634920635</v>
+        <v>0.3277027027027027</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3987730061349694</v>
+        <v>0.3763440860215054</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3019230769230769</v>
+        <v>0.3008547008547008</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.506666666666667</v>
+        <v>1.497835497835498</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.626984126984127</v>
+        <v>0.6554054054054054</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.9751098096632502</v>
+        <v>0.9571984435797666</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8931750741839762</v>
+        <v>0.8886010362694301</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.9828767123287671</v>
+        <v>0.9790419161676647</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.606382978723404</v>
+        <v>1.614678899082569</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.217054263565892</v>
+        <v>1.258064516129032</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.511627906976744</v>
+        <v>4.640552995391705</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.728682170542636</v>
+        <v>5.898617511520738</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2158.68</v>
+        <v>2473.359999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>2149.66</v>
+        <v>2461.320000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>116.250942009434</v>
+        <v>116.4009555848081</v>
       </c>
       <c r="E4" t="n">
-        <v>108.389233646251</v>
+        <v>108.6002632733655</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5389105058365758</v>
+        <v>0.541828793774319</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1373447230282678</v>
+        <v>0.1377410468319559</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2944111776447106</v>
+        <v>0.2883435582822086</v>
       </c>
       <c r="I4" t="n">
-        <v>0.311284046692607</v>
+        <v>0.3098249027237354</v>
       </c>
       <c r="J4" t="n">
-        <v>295</v>
+        <v>348</v>
       </c>
       <c r="K4" t="n">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="L4" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="M4" t="n">
-        <v>311</v>
+        <v>358</v>
       </c>
       <c r="N4" t="n">
-        <v>882</v>
+        <v>1013</v>
       </c>
       <c r="O4" t="n">
-        <v>1128</v>
+        <v>1296</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6270150083379655</v>
+        <v>0.6303501945525292</v>
       </c>
       <c r="Q4" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="R4" t="n">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1561978877153974</v>
+        <v>0.1483463035019455</v>
       </c>
       <c r="T4" t="n">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="U4" t="n">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1534185658699277</v>
+        <v>0.1561284046692607</v>
       </c>
       <c r="W4" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="X4" t="n">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1217342968315731</v>
+        <v>0.1186770428015564</v>
       </c>
       <c r="Z4" t="n">
-        <v>205</v>
+        <v>243</v>
       </c>
       <c r="AA4" t="n">
-        <v>617</v>
+        <v>709</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3429683157309616</v>
+        <v>0.3448443579766537</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7819148936170213</v>
+        <v>0.7816358024691358</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.3807829181494662</v>
+        <v>0.3672131147540983</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.355072463768116</v>
+        <v>0.35202492211838</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.410958904109589</v>
+        <v>0.4057377049180328</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3322528363047001</v>
+        <v>0.3427362482369535</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.563829787234043</v>
+        <v>1.563271604938272</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.7101449275362319</v>
+        <v>0.7040498442367601</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.058612440191387</v>
+        <v>1.076600209863589</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.7622739018087855</v>
+        <v>0.8018433179723502</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.003389830508475</v>
+        <v>1.024316109422492</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.621052631578947</v>
+        <v>1.623762376237624</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.43026706231454</v>
+        <v>1.430051813471503</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.338278931750742</v>
+        <v>5.326424870466322</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.768545994065282</v>
+        <v>6.756476683937824</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>77.09571428571428</v>
+        <v>77.29249999999998</v>
       </c>
       <c r="C5" t="n">
-        <v>76.77357142857144</v>
+        <v>76.91625000000002</v>
       </c>
       <c r="D5" t="n">
-        <v>116.250942009434</v>
+        <v>116.4009555848081</v>
       </c>
       <c r="E5" t="n">
-        <v>108.389233646251</v>
+        <v>108.6002632733655</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5389105058365758</v>
+        <v>0.541828793774319</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1373447230282678</v>
+        <v>0.1377410468319559</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2944111776447106</v>
+        <v>0.2883435582822086</v>
       </c>
       <c r="I5" t="n">
-        <v>0.311284046692607</v>
+        <v>0.3098249027237354</v>
       </c>
       <c r="J5" t="n">
-        <v>10.53571428571429</v>
+        <v>10.875</v>
       </c>
       <c r="K5" t="n">
-        <v>10.57142857142857</v>
+        <v>10.53125</v>
       </c>
       <c r="L5" t="n">
-        <v>5.5</v>
+        <v>5.125</v>
       </c>
       <c r="M5" t="n">
-        <v>11.10714285714286</v>
+        <v>11.1875</v>
       </c>
       <c r="N5" t="n">
-        <v>31.5</v>
+        <v>31.65625</v>
       </c>
       <c r="O5" t="n">
-        <v>40.28571428571428</v>
+        <v>40.5</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6270150083379655</v>
+        <v>0.6303501945525292</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.821428571428572</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>10.03571428571429</v>
+        <v>9.53125</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1561978877153974</v>
+        <v>0.1483463035019455</v>
       </c>
       <c r="T5" t="n">
-        <v>3.5</v>
+        <v>3.53125</v>
       </c>
       <c r="U5" t="n">
-        <v>9.857142857142858</v>
+        <v>10.03125</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1534185658699277</v>
+        <v>0.1561284046692607</v>
       </c>
       <c r="W5" t="n">
-        <v>3.214285714285714</v>
+        <v>3.09375</v>
       </c>
       <c r="X5" t="n">
-        <v>7.821428571428571</v>
+        <v>7.625</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1217342968315731</v>
+        <v>0.1186770428015564</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.321428571428571</v>
+        <v>7.59375</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.03571428571428</v>
+        <v>22.15625</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3429683157309616</v>
+        <v>0.3448443579766537</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7819148936170213</v>
+        <v>0.7816358024691358</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.3807829181494662</v>
+        <v>0.3672131147540983</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3550724637681159</v>
+        <v>0.35202492211838</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4109589041095891</v>
+        <v>0.4057377049180328</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3322528363047001</v>
+        <v>0.3427362482369535</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.563829787234043</v>
+        <v>1.563271604938272</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.7101449275362318</v>
+        <v>0.7040498442367601</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.058612440191388</v>
+        <v>1.076600209863589</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.7622739018087856</v>
+        <v>0.8018433179723502</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.003389830508475</v>
+        <v>1.024316109422492</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.621052631578947</v>
+        <v>1.623762376237624</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.43026706231454</v>
+        <v>1.430051813471503</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.338278931750741</v>
+        <v>5.326424870466322</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.768545994065282</v>
+        <v>6.756476683937824</v>
       </c>
     </row>
     <row r="7">
@@ -1419,67 +1419,67 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>31</v>
+      </c>
+      <c r="C8" t="n">
+        <v>477</v>
+      </c>
+      <c r="D8" t="n">
+        <v>79</v>
+      </c>
+      <c r="E8" t="n">
+        <v>162</v>
+      </c>
+      <c r="F8" t="n">
+        <v>51</v>
+      </c>
+      <c r="G8" t="n">
+        <v>155</v>
+      </c>
+      <c r="H8" t="n">
+        <v>166</v>
+      </c>
+      <c r="I8" t="n">
+        <v>188</v>
+      </c>
+      <c r="J8" t="n">
+        <v>87</v>
+      </c>
+      <c r="K8" t="n">
+        <v>44</v>
+      </c>
+      <c r="L8" t="n">
+        <v>26</v>
+      </c>
+      <c r="M8" t="n">
         <v>27</v>
       </c>
-      <c r="C8" t="n">
-        <v>416</v>
-      </c>
-      <c r="D8" t="n">
-        <v>66</v>
-      </c>
-      <c r="E8" t="n">
-        <v>137</v>
-      </c>
-      <c r="F8" t="n">
-        <v>46</v>
-      </c>
-      <c r="G8" t="n">
-        <v>138</v>
-      </c>
-      <c r="H8" t="n">
-        <v>146</v>
-      </c>
-      <c r="I8" t="n">
-        <v>168</v>
-      </c>
-      <c r="J8" t="n">
-        <v>77</v>
-      </c>
-      <c r="K8" t="n">
-        <v>39</v>
-      </c>
-      <c r="L8" t="n">
-        <v>19</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>23</v>
       </c>
-      <c r="N8" t="n">
-        <v>19</v>
-      </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Q8" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="R8" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="S8" t="n">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="T8" t="n">
-        <v>430</v>
+        <v>503</v>
       </c>
       <c r="U8" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="V8" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="W8" t="n">
         <v>36</v>
@@ -1488,87 +1488,87 @@
         <v>29</v>
       </c>
       <c r="Y8" t="n">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="Z8" t="n">
-        <v>225</v>
+        <v>259</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.8</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="AB8" t="n">
         <v>23</v>
       </c>
       <c r="AC8" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.479</v>
+        <v>0.442</v>
       </c>
       <c r="AE8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AF8" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.281</v>
+        <v>0.333</v>
       </c>
       <c r="AH8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI8" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.346</v>
+        <v>0.323</v>
       </c>
       <c r="AK8" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="AL8" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.33</v>
+        <v>0.331</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>689:45</t>
+          <t>796:29</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>394.92</v>
+        <v>449.72</v>
       </c>
       <c r="AP8" t="n">
         <v>0.491</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.596</v>
+        <v>0.597</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.053</v>
+        <v>1.061</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.116</v>
+        <v>0.111</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.531</v>
+        <v>0.524</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.674</v>
+        <v>1.74</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.264</v>
+        <v>0.26</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.031</v>
+        <v>0.037</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.063</v>
+        <v>0.062</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.113</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="9">
@@ -1578,34 +1578,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F9" t="n">
         <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I9" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J9" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K9" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L9" t="n">
         <v>9</v>
@@ -1620,25 +1620,25 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R9" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="S9" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="T9" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U9" t="n">
         <v>21</v>
       </c>
       <c r="V9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W9" t="n">
         <v>6</v>
@@ -1647,22 +1647,22 @@
         <v>4</v>
       </c>
       <c r="Y9" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Z9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.768</v>
+        <v>0.767</v>
       </c>
       <c r="AB9" t="n">
         <v>5</v>
       </c>
       <c r="AC9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.417</v>
+        <v>0.357</v>
       </c>
       <c r="AE9" t="n">
         <v>3</v>
@@ -1677,57 +1677,57 @@
         <v>9</v>
       </c>
       <c r="AI9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.529</v>
       </c>
       <c r="AK9" t="n">
         <v>6</v>
       </c>
       <c r="AL9" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.128</v>
+        <v>0.115</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>494:09</t>
+          <t>540:07</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>160.52</v>
+        <v>172.84</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.415</v>
+        <v>0.393</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.474</v>
+        <v>0.453</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.748</v>
+        <v>0.717</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.212</v>
+        <v>0.208</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.241</v>
+        <v>0.24</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.324</v>
+        <v>1.361</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.15</v>
+        <v>0.147</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.021</v>
+        <v>0.019</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.106</v>
+        <v>0.104</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="10">
@@ -1737,156 +1737,156 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>341</v>
+        <v>378</v>
       </c>
       <c r="D10" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="E10" t="n">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="F10" t="n">
+        <v>31</v>
+      </c>
+      <c r="G10" t="n">
+        <v>84</v>
+      </c>
+      <c r="H10" t="n">
+        <v>79</v>
+      </c>
+      <c r="I10" t="n">
+        <v>93</v>
+      </c>
+      <c r="J10" t="n">
+        <v>32</v>
+      </c>
+      <c r="K10" t="n">
+        <v>128</v>
+      </c>
+      <c r="L10" t="n">
+        <v>42</v>
+      </c>
+      <c r="M10" t="n">
+        <v>24</v>
+      </c>
+      <c r="N10" t="n">
+        <v>36</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>48</v>
+      </c>
+      <c r="R10" t="n">
+        <v>88</v>
+      </c>
+      <c r="S10" t="n">
+        <v>89</v>
+      </c>
+      <c r="T10" t="n">
+        <v>434</v>
+      </c>
+      <c r="U10" t="n">
+        <v>48</v>
+      </c>
+      <c r="V10" t="n">
+        <v>48</v>
+      </c>
+      <c r="W10" t="n">
+        <v>28</v>
+      </c>
+      <c r="X10" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>144</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>187</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>54</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>47</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="AK10" t="n">
         <v>26</v>
       </c>
-      <c r="G10" t="n">
-        <v>70</v>
-      </c>
-      <c r="H10" t="n">
-        <v>75</v>
-      </c>
-      <c r="I10" t="n">
-        <v>89</v>
-      </c>
-      <c r="J10" t="n">
-        <v>28</v>
-      </c>
-      <c r="K10" t="n">
-        <v>115</v>
-      </c>
-      <c r="L10" t="n">
-        <v>36</v>
-      </c>
-      <c r="M10" t="n">
-        <v>20</v>
-      </c>
-      <c r="N10" t="n">
-        <v>34</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>40</v>
-      </c>
-      <c r="R10" t="n">
-        <v>76</v>
-      </c>
-      <c r="S10" t="n">
-        <v>86</v>
-      </c>
-      <c r="T10" t="n">
-        <v>404</v>
-      </c>
-      <c r="U10" t="n">
-        <v>40</v>
-      </c>
-      <c r="V10" t="n">
-        <v>42</v>
-      </c>
-      <c r="W10" t="n">
-        <v>24</v>
-      </c>
-      <c r="X10" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>134</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>173</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>22</v>
-      </c>
       <c r="AL10" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.415</v>
+        <v>0.394</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>682:22</t>
+          <t>784:24</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>325.16</v>
+        <v>367.92</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.541</v>
+        <v>0.536</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.598</v>
+        <v>0.591</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.049</v>
+        <v>1.027</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.123</v>
+        <v>0.13</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.305</v>
+        <v>0.283</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.7</v>
+        <v>0.667</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.219</v>
+        <v>0.216</v>
       </c>
       <c r="AW10" t="n">
         <v>0.06</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.188</v>
+        <v>0.183</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.042</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="11">
@@ -1896,43 +1896,43 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="D11" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E11" t="n">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="F11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G11" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H11" t="n">
         <v>41</v>
       </c>
       <c r="I11" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J11" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="K11" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="L11" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M11" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1944,108 +1944,108 @@
         <v>50</v>
       </c>
       <c r="R11" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="S11" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="T11" t="n">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="U11" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="V11" t="n">
         <v>33</v>
       </c>
       <c r="W11" t="n">
+        <v>4</v>
+      </c>
+      <c r="X11" t="n">
         <v>2</v>
       </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
       <c r="Y11" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Z11" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.612</v>
+        <v>0.606</v>
       </c>
       <c r="AB11" t="n">
         <v>14</v>
       </c>
       <c r="AC11" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.286</v>
+        <v>0.269</v>
       </c>
       <c r="AE11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF11" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.333</v>
+        <v>0.317</v>
       </c>
       <c r="AH11" t="n">
         <v>2</v>
       </c>
       <c r="AI11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AK11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL11" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.263</v>
+        <v>0.266</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>469:31</t>
+          <t>532:00</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>319.84</v>
+        <v>343.72</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.403</v>
+        <v>0.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.439</v>
+        <v>0.432</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.741</v>
+        <v>0.739</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.156</v>
+        <v>0.145</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.169</v>
+        <v>0.154</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.314</v>
+        <v>0.297</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.055</v>
+        <v>0.057</v>
       </c>
       <c r="AX11" t="n">
         <v>0.133</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="12">
@@ -2055,156 +2055,156 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C12" t="n">
-        <v>259</v>
+        <v>312</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="E12" t="n">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="F12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G12" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="H12" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="I12" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="J12" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="K12" t="n">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="L12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="Q12" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="R12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="S12" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="T12" t="n">
-        <v>337</v>
+        <v>408</v>
       </c>
       <c r="U12" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="V12" t="n">
         <v>25</v>
       </c>
       <c r="W12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="X12" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>129</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>173</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="AB12" t="n">
         <v>10</v>
       </c>
-      <c r="Y12" t="n">
-        <v>111</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>142</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0.782</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>8</v>
-      </c>
       <c r="AC12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.444</v>
+        <v>0.435</v>
       </c>
       <c r="AE12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.208</v>
+        <v>0.259</v>
       </c>
       <c r="AH12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.381</v>
+        <v>0.4</v>
       </c>
       <c r="AK12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AL12" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.327</v>
+        <v>0.322</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>630:33</t>
+          <t>735:20</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>254.44</v>
+        <v>307.6</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.556</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.612</v>
+        <v>0.608</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.018</v>
+        <v>1.014</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.169</v>
+        <v>0.166</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.343</v>
+        <v>0.309</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.698</v>
+        <v>1.706</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.186</v>
+        <v>0.192</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.034</v>
+        <v>0.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.142</v>
+        <v>0.156</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.104</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="13">
@@ -2363,7 +2363,7 @@
         <v>0.061</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="14">
@@ -2373,40 +2373,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
+        <v>14</v>
+      </c>
+      <c r="E14" t="n">
+        <v>27</v>
+      </c>
+      <c r="F14" t="n">
         <v>10</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
+        <v>34</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="n">
         <v>17</v>
       </c>
-      <c r="F14" t="n">
-        <v>8</v>
-      </c>
-      <c r="G14" t="n">
-        <v>24</v>
-      </c>
-      <c r="H14" t="n">
-        <v>7</v>
-      </c>
-      <c r="I14" t="n">
-        <v>7</v>
-      </c>
       <c r="J14" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="K14" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="L14" t="n">
         <v>5</v>
       </c>
       <c r="M14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2415,114 +2415,114 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="Q14" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="T14" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V14" t="n">
         <v>8</v>
       </c>
       <c r="W14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="Z14" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.9</v>
+        <v>0.667</v>
       </c>
       <c r="AB14" t="n">
         <v>1</v>
       </c>
       <c r="AC14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF14" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.636</v>
+        <v>0.6</v>
       </c>
       <c r="AH14" t="n">
         <v>1</v>
       </c>
       <c r="AI14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL14" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.304</v>
+        <v>0.281</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>176:38</t>
+          <t>255:09</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>58.08</v>
+        <v>92.48</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.537</v>
+        <v>0.475</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.578</v>
+        <v>0.511</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.878</v>
+        <v>0.757</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.241</v>
+        <v>0.26</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.171</v>
+        <v>0.197</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.571</v>
+        <v>2.167</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.151</v>
+        <v>0.167</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.032</v>
+        <v>0.022</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.139</v>
+        <v>0.141</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.047</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="15">
@@ -2532,34 +2532,34 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E15" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F15" t="n">
         <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H15" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I15" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="J15" t="n">
         <v>17</v>
       </c>
       <c r="K15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L15" t="n">
         <v>28</v>
@@ -2574,19 +2574,19 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R15" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="S15" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="T15" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="U15" t="n">
         <v>20</v>
@@ -2601,10 +2601,10 @@
         <v>8</v>
       </c>
       <c r="Y15" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="Z15" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="AA15" t="n">
         <v>0.786</v>
@@ -2622,10 +2622,10 @@
         <v>3</v>
       </c>
       <c r="AF15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.375</v>
+        <v>0.333</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
@@ -2640,48 +2640,48 @@
         <v>4</v>
       </c>
       <c r="AL15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.364</v>
+        <v>0.333</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>338:10</t>
+          <t>349:33</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>146.12</v>
+        <v>151.88</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.699</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.731</v>
+        <v>0.724</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.252</v>
+        <v>1.238</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.144</v>
+        <v>0.145</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.57</v>
+        <v>0.583</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.773</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.199</v>
+        <v>0.2</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.093</v>
+        <v>0.09</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.178</v>
+        <v>0.177</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.023</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="16">
@@ -2691,16 +2691,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C16" t="n">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="D16" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="E16" t="n">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2709,25 +2709,25 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I16" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="J16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K16" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="L16" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="M16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N16" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2739,19 +2739,19 @@
         <v>27</v>
       </c>
       <c r="R16" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="S16" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="T16" t="n">
-        <v>174</v>
+        <v>219</v>
       </c>
       <c r="U16" t="n">
         <v>8</v>
       </c>
       <c r="V16" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="W16" t="n">
         <v>6</v>
@@ -2760,31 +2760,31 @@
         <v>3</v>
       </c>
       <c r="Y16" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="Z16" t="n">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.853</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="AB16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.35</v>
+        <v>0.381</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.286</v>
+        <v>0.375</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
@@ -2806,41 +2806,41 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>341:57</t>
+          <t>396:44</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>127.16</v>
+        <v>148.32</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.735</v>
+        <v>0.765</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.754</v>
+        <v>0.762</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.187</v>
+        <v>1.247</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.212</v>
+        <v>0.182</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.349</v>
+        <v>0.357</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.259</v>
+        <v>0.333</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.171</v>
+        <v>0.172</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.135</v>
+        <v>0.13</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.134</v>
+        <v>0.147</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="17">
@@ -2850,22 +2850,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H17" t="n">
         <v>4</v>
@@ -2874,16 +2874,16 @@
         <v>8</v>
       </c>
       <c r="J17" t="n">
+        <v>11</v>
+      </c>
+      <c r="K17" t="n">
         <v>6</v>
       </c>
-      <c r="K17" t="n">
-        <v>3</v>
-      </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
         <v>3</v>
@@ -2892,25 +2892,25 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
+        <v>12</v>
+      </c>
+      <c r="S17" t="n">
         <v>8</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
+        <v>29</v>
+      </c>
+      <c r="U17" t="n">
         <v>4</v>
       </c>
-      <c r="T17" t="n">
-        <v>14</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W17" t="n">
         <v>3</v>
@@ -2919,19 +2919,19 @@
         <v>3</v>
       </c>
       <c r="Y17" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.583</v>
+        <v>0.611</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -2949,57 +2949,57 @@
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM17" t="n">
         <v>0.5</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>35:54</t>
+          <t>71:35</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>13.52</v>
+        <v>29.52</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.476</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.489</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.962</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.148</v>
+        <v>0.169</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.5</v>
+        <v>0.19</v>
       </c>
       <c r="AU17" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.173</v>
+        <v>0.19</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>0.078</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.008</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="18">
@@ -3009,34 +3009,34 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C18" t="n">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="D18" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E18" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="F18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G18" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I18" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K18" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L18" t="n">
         <v>18</v>
@@ -3045,46 +3045,46 @@
         <v>11</v>
       </c>
       <c r="N18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R18" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T18" t="n">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="U18" t="n">
+        <v>31</v>
+      </c>
+      <c r="V18" t="n">
         <v>25</v>
       </c>
-      <c r="V18" t="n">
-        <v>22</v>
-      </c>
       <c r="W18" t="n">
+        <v>8</v>
+      </c>
+      <c r="X18" t="n">
         <v>5</v>
       </c>
-      <c r="X18" t="n">
-        <v>3</v>
-      </c>
       <c r="Y18" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="Z18" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.643</v>
+        <v>0.681</v>
       </c>
       <c r="AB18" t="n">
         <v>4</v>
@@ -3099,66 +3099,66 @@
         <v>2</v>
       </c>
       <c r="AF18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AH18" t="n">
         <v>7</v>
       </c>
       <c r="AI18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.318</v>
+        <v>0.292</v>
       </c>
       <c r="AK18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AL18" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.367</v>
+        <v>0.382</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>401:07</t>
+          <t>448:22</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>120.24</v>
+        <v>139.56</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.596</v>
+        <v>0.612</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.591</v>
+        <v>0.608</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.065</v>
+        <v>1.103</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.1</v>
+        <v>0.093</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.101</v>
+        <v>0.103</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.333</v>
+        <v>1.308</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.138</v>
+        <v>0.143</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.051</v>
+        <v>0.045</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.103</v>
+        <v>0.098</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="19">
@@ -3168,37 +3168,37 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C19" t="n">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="D19" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E19" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="F19" t="n">
+        <v>19</v>
+      </c>
+      <c r="G19" t="n">
+        <v>64</v>
+      </c>
+      <c r="H19" t="n">
+        <v>13</v>
+      </c>
+      <c r="I19" t="n">
+        <v>21</v>
+      </c>
+      <c r="J19" t="n">
+        <v>28</v>
+      </c>
+      <c r="K19" t="n">
+        <v>52</v>
+      </c>
+      <c r="L19" t="n">
         <v>16</v>
-      </c>
-      <c r="G19" t="n">
-        <v>54</v>
-      </c>
-      <c r="H19" t="n">
-        <v>12</v>
-      </c>
-      <c r="I19" t="n">
-        <v>19</v>
-      </c>
-      <c r="J19" t="n">
-        <v>22</v>
-      </c>
-      <c r="K19" t="n">
-        <v>47</v>
-      </c>
-      <c r="L19" t="n">
-        <v>13</v>
       </c>
       <c r="M19" t="n">
         <v>12</v>
@@ -3210,114 +3210,114 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>32</v>
+      </c>
+      <c r="R19" t="n">
+        <v>30</v>
+      </c>
+      <c r="S19" t="n">
         <v>28</v>
       </c>
-      <c r="Q19" t="n">
-        <v>28</v>
-      </c>
-      <c r="R19" t="n">
-        <v>24</v>
-      </c>
-      <c r="S19" t="n">
-        <v>26</v>
-      </c>
       <c r="T19" t="n">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="U19" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="V19" t="n">
         <v>6</v>
       </c>
       <c r="W19" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="X19" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>31</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH19" t="n">
         <v>9</v>
       </c>
-      <c r="Y19" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>35</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>8</v>
-      </c>
       <c r="AI19" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.421</v>
+        <v>0.391</v>
       </c>
       <c r="AK19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AL19" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.229</v>
+        <v>0.244</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>313:34</t>
+          <t>359:43</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>130.36</v>
+        <v>158.24</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.489</v>
+        <v>0.509</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.508</v>
+        <v>0.523</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.798</v>
+        <v>0.834</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.215</v>
+        <v>0.202</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.128</v>
+        <v>0.111</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.786</v>
+        <v>0.875</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.191</v>
+        <v>0.202</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.047</v>
+        <v>0.05</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.168</v>
+        <v>0.162</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.029</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="20">
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C20" t="n">
         <v>158</v>
@@ -3342,7 +3342,7 @@
         <v>34</v>
       </c>
       <c r="G20" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H20" t="n">
         <v>16</v>
@@ -3381,7 +3381,7 @@
         <v>18</v>
       </c>
       <c r="T20" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="U20" t="n">
         <v>18</v>
@@ -3426,10 +3426,10 @@
         <v>15</v>
       </c>
       <c r="AI20" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.469</v>
+        <v>0.455</v>
       </c>
       <c r="AK20" t="n">
         <v>19</v>
@@ -3442,41 +3442,41 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>480:19</t>
+          <t>491:07</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>145.24</v>
+        <v>146.24</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.555</v>
+        <v>0.55</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.576</v>
+        <v>0.571</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.088</v>
+        <v>1.08</v>
       </c>
       <c r="AS20" t="n">
         <v>0.055</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.125</v>
+        <v>0.124</v>
       </c>
       <c r="AU20" t="n">
         <v>2</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.139</v>
+        <v>0.137</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.038</v>
+        <v>0.036</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.147</v>
+        <v>0.144</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.022</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="21">
@@ -3486,16 +3486,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="D21" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="E21" t="n">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -3504,82 +3504,82 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I21" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J21" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="K21" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="L21" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="M21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N21" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="Q21" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="R21" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="S21" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="T21" t="n">
-        <v>165</v>
+        <v>231</v>
       </c>
       <c r="U21" t="n">
         <v>6</v>
       </c>
       <c r="V21" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="W21" t="n">
+        <v>6</v>
+      </c>
+      <c r="X21" t="n">
         <v>4</v>
       </c>
-      <c r="X21" t="n">
-        <v>3</v>
-      </c>
       <c r="Y21" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="Z21" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.679</v>
+        <v>0.724</v>
       </c>
       <c r="AB21" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AC21" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.297</v>
+        <v>0.333</v>
       </c>
       <c r="AE21" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AF21" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.214</v>
+        <v>0.333</v>
       </c>
       <c r="AH21" t="n">
         <v>0</v>
@@ -3601,41 +3601,41 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>368:00</t>
+          <t>461:51</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>124.6</v>
+        <v>162.8</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.438</v>
+        <v>0.513</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.497</v>
+        <v>0.555</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.851</v>
+        <v>0.946</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.144</v>
+        <v>0.147</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.315</v>
+        <v>0.269</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.333</v>
+        <v>2.125</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.156</v>
+        <v>0.162</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.089</v>
+        <v>0.082</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.128</v>
+        <v>0.134</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.056</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="22">
@@ -3950,7 +3950,7 @@
         <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.186</v>
+        <v>0.187</v>
       </c>
       <c r="AY23" t="n">
         <v>0.001</v>
@@ -4122,7 +4122,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -4149,10 +4149,10 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="L25" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -4277,157 +4277,157 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>2673</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>678</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1243</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>771</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>579</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>762</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>546</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>812</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>434</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>407</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>777</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>707</v>
       </c>
       <c r="T26" t="n">
-        <v>41</v>
+        <v>3002</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>343</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>327</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1038</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1386</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>0.749</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>323</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>0.378</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>296</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>0.328</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>0.376</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>585</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>0.301</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>6400:00</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>27</v>
+        <v>2783.28</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>0.569</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>0.156</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>0.287</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>1.258</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>0.142</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
@@ -4436,157 +4436,157 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C27" t="n">
-        <v>2330</v>
+        <v>2865</v>
       </c>
       <c r="D27" t="n">
-        <v>569</v>
+        <v>601</v>
       </c>
       <c r="E27" t="n">
-        <v>1063</v>
+        <v>1103</v>
       </c>
       <c r="F27" t="n">
-        <v>222</v>
+        <v>342</v>
       </c>
       <c r="G27" t="n">
-        <v>683</v>
+        <v>953</v>
       </c>
       <c r="H27" t="n">
-        <v>526</v>
+        <v>637</v>
       </c>
       <c r="I27" t="n">
-        <v>681</v>
+        <v>819</v>
       </c>
       <c r="J27" t="n">
-        <v>471</v>
+        <v>552</v>
       </c>
       <c r="K27" t="n">
-        <v>707</v>
+        <v>810</v>
       </c>
       <c r="L27" t="n">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="M27" t="n">
-        <v>189</v>
+        <v>230</v>
       </c>
       <c r="N27" t="n">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Q27" t="n">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="R27" t="n">
-        <v>689</v>
+        <v>715</v>
       </c>
       <c r="S27" t="n">
-        <v>626</v>
+        <v>760</v>
       </c>
       <c r="T27" t="n">
-        <v>2611</v>
+        <v>3351</v>
       </c>
       <c r="U27" t="n">
-        <v>301</v>
+        <v>348</v>
       </c>
       <c r="V27" t="n">
-        <v>287</v>
+        <v>337</v>
       </c>
       <c r="W27" t="n">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="X27" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="Y27" t="n">
-        <v>904</v>
+        <v>1013</v>
       </c>
       <c r="Z27" t="n">
-        <v>1200</v>
+        <v>1296</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.753</v>
+        <v>0.782</v>
       </c>
       <c r="AB27" t="n">
         <v>112</v>
       </c>
       <c r="AC27" t="n">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.384</v>
+        <v>0.367</v>
       </c>
       <c r="AE27" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AF27" t="n">
-        <v>252</v>
+        <v>321</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.313</v>
+        <v>0.352</v>
       </c>
       <c r="AH27" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="AI27" t="n">
-        <v>163</v>
+        <v>244</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.399</v>
+        <v>0.406</v>
       </c>
       <c r="AK27" t="n">
-        <v>157</v>
+        <v>243</v>
       </c>
       <c r="AL27" t="n">
-        <v>520</v>
+        <v>709</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.302</v>
+        <v>0.343</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>5600:00</t>
+          <t>6400:00</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>2432.64</v>
+        <v>2802.36</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.517</v>
+        <v>0.542</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.57</v>
+        <v>0.593</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.958</v>
+        <v>1.022</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.159</v>
+        <v>0.138</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.301</v>
+        <v>0.31</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.217</v>
+        <v>1.43</v>
       </c>
       <c r="AV27" t="n">
         <v>0.2</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.059</v>
+        <v>0.058</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.141</v>
+        <v>0.142</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -4595,1430 +4595,1430 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>28</v>
-      </c>
-      <c r="C28" t="n">
-        <v>2499</v>
-      </c>
-      <c r="D28" t="n">
-        <v>527</v>
-      </c>
-      <c r="E28" t="n">
-        <v>963</v>
-      </c>
-      <c r="F28" t="n">
-        <v>295</v>
-      </c>
-      <c r="G28" t="n">
-        <v>836</v>
-      </c>
-      <c r="H28" t="n">
-        <v>560</v>
-      </c>
-      <c r="I28" t="n">
-        <v>722</v>
-      </c>
-      <c r="J28" t="n">
-        <v>482</v>
-      </c>
-      <c r="K28" t="n">
-        <v>700</v>
-      </c>
-      <c r="L28" t="n">
-        <v>295</v>
-      </c>
-      <c r="M28" t="n">
-        <v>202</v>
-      </c>
-      <c r="N28" t="n">
-        <v>184</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>337</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>311</v>
-      </c>
-      <c r="R28" t="n">
-        <v>635</v>
-      </c>
-      <c r="S28" t="n">
-        <v>672</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2923</v>
-      </c>
-      <c r="U28" t="n">
-        <v>295</v>
-      </c>
-      <c r="V28" t="n">
-        <v>296</v>
-      </c>
-      <c r="W28" t="n">
-        <v>154</v>
-      </c>
-      <c r="X28" t="n">
-        <v>95</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>882</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1128</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0.782</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>107</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>281</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0.381</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>98</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>276</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>90</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>219</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>205</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>617</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0.332</v>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>5600:00</t>
-        </is>
-      </c>
-      <c r="AO28" t="n">
-        <v>2453.68</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0.539</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.018</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0.311</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr"/>
-      <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr"/>
-      <c r="AO29" t="inlineStr"/>
-      <c r="AP29" t="inlineStr"/>
-      <c r="AQ29" t="inlineStr"/>
-      <c r="AR29" t="inlineStr"/>
-      <c r="AS29" t="inlineStr"/>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AU29" t="inlineStr"/>
-      <c r="AV29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr"/>
-      <c r="AX29" t="inlineStr"/>
-      <c r="AY29" t="inlineStr"/>
+          <t>#1 J. BATEMON (Per Game)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>31</v>
+      </c>
+      <c r="C29" t="n">
+        <v>15.387</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.548</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5.226</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.645</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>5.355</v>
+      </c>
+      <c r="I29" t="n">
+        <v>6.065</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.806</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.613</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.613</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.581</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5.097</v>
+      </c>
+      <c r="T29" t="n">
+        <v>503</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.387</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.323</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.161</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>6.742</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>8.355</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.677</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.258</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.323</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>25:41</t>
+        </is>
+      </c>
+      <c r="AO29" t="n">
+        <v>14.507</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.061</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0.114</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>#1 J. BATEMON (Per Game)</t>
+          <t>#2 C. WALDEN (Per Game)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C30" t="n">
-        <v>15.407</v>
+        <v>3.875</v>
       </c>
       <c r="D30" t="n">
-        <v>2.444</v>
+        <v>0.781</v>
       </c>
       <c r="E30" t="n">
-        <v>5.074</v>
+        <v>1.625</v>
       </c>
       <c r="F30" t="n">
-        <v>1.704</v>
+        <v>0.469</v>
       </c>
       <c r="G30" t="n">
-        <v>5.111</v>
+        <v>2.156</v>
       </c>
       <c r="H30" t="n">
-        <v>5.407</v>
+        <v>0.906</v>
       </c>
       <c r="I30" t="n">
-        <v>6.222</v>
+        <v>1.125</v>
       </c>
       <c r="J30" t="n">
-        <v>2.852</v>
+        <v>1.531</v>
       </c>
       <c r="K30" t="n">
-        <v>1.444</v>
+        <v>1.562</v>
       </c>
       <c r="L30" t="n">
-        <v>0.704</v>
+        <v>0.281</v>
       </c>
       <c r="M30" t="n">
-        <v>0.852</v>
+        <v>0.656</v>
       </c>
       <c r="N30" t="n">
-        <v>0.704</v>
+        <v>0.25</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.704</v>
+        <v>1.125</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.704</v>
+        <v>1.125</v>
       </c>
       <c r="R30" t="n">
-        <v>2.556</v>
+        <v>2.062</v>
       </c>
       <c r="S30" t="n">
-        <v>5.074</v>
+        <v>1.312</v>
       </c>
       <c r="T30" t="n">
-        <v>430</v>
+        <v>113</v>
       </c>
       <c r="U30" t="n">
-        <v>2.667</v>
+        <v>0.656</v>
       </c>
       <c r="V30" t="n">
-        <v>1.222</v>
+        <v>0.375</v>
       </c>
       <c r="W30" t="n">
-        <v>1.333</v>
+        <v>0.188</v>
       </c>
       <c r="X30" t="n">
-        <v>1.074</v>
+        <v>0.125</v>
       </c>
       <c r="Y30" t="n">
-        <v>6.667</v>
+        <v>1.438</v>
       </c>
       <c r="Z30" t="n">
-        <v>8.333</v>
+        <v>1.875</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.852</v>
+        <v>0.156</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.778</v>
+        <v>0.438</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.479</v>
+        <v>0.357</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.333</v>
+        <v>0.094</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.185</v>
+        <v>0.438</v>
       </c>
       <c r="AG30" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AH30" t="n">
         <v>0.281</v>
       </c>
-      <c r="AH30" t="n">
-        <v>0.333</v>
-      </c>
       <c r="AI30" t="n">
-        <v>0.963</v>
+        <v>0.531</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.346</v>
+        <v>0.529</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.37</v>
+        <v>0.188</v>
       </c>
       <c r="AL30" t="n">
-        <v>4.148</v>
+        <v>1.625</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.33</v>
+        <v>0.115</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>25:32</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>14.627</v>
+        <v>5.401</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.491</v>
+        <v>0.393</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.596</v>
+        <v>0.453</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.053</v>
+        <v>0.717</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.116</v>
+        <v>0.208</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.531</v>
+        <v>0.24</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.674</v>
+        <v>1.361</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.264</v>
+        <v>0.147</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.031</v>
+        <v>0.019</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.063</v>
+        <v>0.104</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.118</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#2 C. WALDEN (Per Game)</t>
+          <t>#3 M. EJIM (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C31" t="n">
-        <v>4.286</v>
+        <v>12.194</v>
       </c>
       <c r="D31" t="n">
-        <v>0.857</v>
+        <v>3.323</v>
       </c>
       <c r="E31" t="n">
-        <v>1.75</v>
+        <v>6.29</v>
       </c>
       <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.548</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.129</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.355</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.161</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.548</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.548</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.839</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.871</v>
+      </c>
+      <c r="T31" t="n">
+        <v>434</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.548</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.548</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>4.645</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>6.032</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.742</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.516</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.581</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2.129</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>25:18</t>
+        </is>
+      </c>
+      <c r="AO31" t="n">
+        <v>11.868</v>
+      </c>
+      <c r="AP31" t="n">
         <v>0.536</v>
       </c>
-      <c r="G31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.964</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1.179</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1.607</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1.679</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0.321</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.214</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.214</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2.179</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1.357</v>
-      </c>
-      <c r="T31" t="n">
-        <v>114</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.536</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0.768</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0.321</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0.5629999999999999</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.679</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>17:38</t>
-        </is>
-      </c>
-      <c r="AO31" t="n">
-        <v>5.733</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0.415</v>
-      </c>
       <c r="AQ31" t="n">
-        <v>0.474</v>
+        <v>0.591</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.748</v>
+        <v>1.027</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.212</v>
+        <v>0.13</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.241</v>
+        <v>0.283</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.324</v>
+        <v>0.667</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.15</v>
+        <v>0.216</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.021</v>
+        <v>0.06</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.106</v>
+        <v>0.183</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.06</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#3 M. EJIM (Per Game)</t>
+          <t>#4 C. AGADA (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C32" t="n">
-        <v>12.63</v>
+        <v>7.938</v>
       </c>
       <c r="D32" t="n">
-        <v>3.481</v>
+        <v>2.25</v>
       </c>
       <c r="E32" t="n">
-        <v>6.519</v>
+        <v>5.656</v>
       </c>
       <c r="F32" t="n">
-        <v>0.963</v>
+        <v>0.719</v>
       </c>
       <c r="G32" t="n">
-        <v>2.593</v>
+        <v>2.656</v>
       </c>
       <c r="H32" t="n">
-        <v>2.778</v>
+        <v>1.281</v>
       </c>
       <c r="I32" t="n">
-        <v>3.296</v>
+        <v>1.969</v>
       </c>
       <c r="J32" t="n">
-        <v>1.037</v>
+        <v>2.031</v>
       </c>
       <c r="K32" t="n">
-        <v>4.259</v>
+        <v>1.969</v>
       </c>
       <c r="L32" t="n">
-        <v>1.333</v>
+        <v>0.844</v>
       </c>
       <c r="M32" t="n">
-        <v>0.741</v>
+        <v>1.031</v>
       </c>
       <c r="N32" t="n">
-        <v>1.259</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.481</v>
+        <v>1.562</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.481</v>
+        <v>1.562</v>
       </c>
       <c r="R32" t="n">
-        <v>2.815</v>
+        <v>3.094</v>
       </c>
       <c r="S32" t="n">
-        <v>3.185</v>
+        <v>2.062</v>
       </c>
       <c r="T32" t="n">
-        <v>404</v>
+        <v>184</v>
       </c>
       <c r="U32" t="n">
-        <v>1.481</v>
+        <v>1.156</v>
       </c>
       <c r="V32" t="n">
-        <v>1.556</v>
+        <v>1.031</v>
       </c>
       <c r="W32" t="n">
-        <v>0.889</v>
+        <v>0.125</v>
       </c>
       <c r="X32" t="n">
-        <v>0.556</v>
+        <v>0.062</v>
       </c>
       <c r="Y32" t="n">
-        <v>4.963</v>
+        <v>2.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>6.407</v>
+        <v>4.125</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.775</v>
+        <v>0.606</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.438</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.852</v>
+        <v>1.625</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.44</v>
+        <v>0.269</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.481</v>
+        <v>0.594</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.556</v>
+        <v>1.875</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.31</v>
+        <v>0.317</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.148</v>
+        <v>0.062</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.63</v>
+        <v>0.188</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.235</v>
+        <v>0.333</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.656</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.963</v>
+        <v>2.469</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.415</v>
+        <v>0.266</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>25:16</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>12.043</v>
+        <v>10.741</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.541</v>
+        <v>0.4</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.598</v>
+        <v>0.432</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.049</v>
+        <v>0.739</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.123</v>
+        <v>0.145</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.305</v>
+        <v>0.154</v>
       </c>
       <c r="AU32" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.219</v>
+        <v>0.297</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.06</v>
+        <v>0.057</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.188</v>
+        <v>0.133</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.044</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#4 C. AGADA (Per Game)</t>
+          <t>#5 O. PAULÍ (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>8.464</v>
+        <v>9.75</v>
       </c>
       <c r="D33" t="n">
-        <v>2.321</v>
+        <v>2.469</v>
       </c>
       <c r="E33" t="n">
-        <v>5.821</v>
+        <v>4.156</v>
       </c>
       <c r="F33" t="n">
-        <v>0.786</v>
+        <v>0.906</v>
       </c>
       <c r="G33" t="n">
-        <v>2.857</v>
+        <v>2.625</v>
       </c>
       <c r="H33" t="n">
-        <v>1.464</v>
+        <v>2.094</v>
       </c>
       <c r="I33" t="n">
-        <v>2.179</v>
+        <v>2.812</v>
       </c>
       <c r="J33" t="n">
-        <v>2.179</v>
+        <v>2.719</v>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>3.188</v>
       </c>
       <c r="L33" t="n">
-        <v>0.821</v>
+        <v>0.625</v>
       </c>
       <c r="M33" t="n">
-        <v>1.107</v>
+        <v>0.625</v>
       </c>
       <c r="N33" t="n">
-        <v>0.571</v>
+        <v>0.25</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.786</v>
+        <v>1.594</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.786</v>
+        <v>1.594</v>
       </c>
       <c r="R33" t="n">
-        <v>3.25</v>
+        <v>1.438</v>
       </c>
       <c r="S33" t="n">
-        <v>2.286</v>
+        <v>2.75</v>
       </c>
       <c r="T33" t="n">
-        <v>171</v>
+        <v>408</v>
       </c>
       <c r="U33" t="n">
-        <v>1.214</v>
+        <v>1.219</v>
       </c>
       <c r="V33" t="n">
-        <v>1.179</v>
+        <v>0.781</v>
       </c>
       <c r="W33" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="X33" t="n">
-        <v>0.036</v>
+        <v>0.406</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.643</v>
+        <v>4.031</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.321</v>
+        <v>5.406</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.612</v>
+        <v>0.746</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.5</v>
+        <v>0.312</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.75</v>
+        <v>0.719</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.286</v>
+        <v>0.435</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.643</v>
+        <v>0.219</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.929</v>
+        <v>0.844</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.333</v>
+        <v>0.259</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.312</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.143</v>
+        <v>0.781</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.714</v>
+        <v>0.594</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.714</v>
+        <v>1.844</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.263</v>
+        <v>0.322</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>11.423</v>
+        <v>9.612</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.403</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.439</v>
+        <v>0.608</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.741</v>
+        <v>1.014</v>
       </c>
       <c r="AS33" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>1.706</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AX33" t="n">
         <v>0.156</v>
       </c>
-      <c r="AT33" t="n">
-        <v>0.169</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0.133</v>
-      </c>
       <c r="AY33" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#5 O. PAULÍ (Per Game)</t>
+          <t>#6 D. GARCÍA (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C34" t="n">
-        <v>9.25</v>
+        <v>5.833</v>
       </c>
       <c r="D34" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="E34" t="n">
         <v>2.25</v>
       </c>
-      <c r="E34" t="n">
-        <v>3.857</v>
-      </c>
       <c r="F34" t="n">
-        <v>0.857</v>
+        <v>0.833</v>
       </c>
       <c r="G34" t="n">
-        <v>2.5</v>
+        <v>2.833</v>
       </c>
       <c r="H34" t="n">
-        <v>2.179</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>2.714</v>
+        <v>1.417</v>
       </c>
       <c r="J34" t="n">
-        <v>2.607</v>
+        <v>4.333</v>
       </c>
       <c r="K34" t="n">
-        <v>2.857</v>
+        <v>2.667</v>
       </c>
       <c r="L34" t="n">
-        <v>0.679</v>
+        <v>0.417</v>
       </c>
       <c r="M34" t="n">
-        <v>0.607</v>
+        <v>1.167</v>
       </c>
       <c r="N34" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.536</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.536</v>
+        <v>2</v>
       </c>
       <c r="R34" t="n">
-        <v>1.464</v>
+        <v>3.667</v>
       </c>
       <c r="S34" t="n">
-        <v>2.571</v>
+        <v>2.167</v>
       </c>
       <c r="T34" t="n">
-        <v>337</v>
+        <v>89</v>
       </c>
       <c r="U34" t="n">
-        <v>1.107</v>
+        <v>0.583</v>
       </c>
       <c r="V34" t="n">
-        <v>0.893</v>
+        <v>0.667</v>
       </c>
       <c r="W34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AE34" t="n">
         <v>0.75</v>
       </c>
-      <c r="X34" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>3.964</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>5.071</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0.782</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0.643</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0.179</v>
-      </c>
       <c r="AF34" t="n">
-        <v>0.857</v>
+        <v>1.25</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.208</v>
+        <v>0.6</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.286</v>
+        <v>0.083</v>
       </c>
       <c r="AI34" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK34" t="n">
         <v>0.75</v>
       </c>
-      <c r="AJ34" t="n">
-        <v>0.381</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0.571</v>
-      </c>
       <c r="AL34" t="n">
-        <v>1.75</v>
+        <v>2.667</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.327</v>
+        <v>0.281</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>9.087</v>
+        <v>7.707</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.556</v>
+        <v>0.475</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.612</v>
+        <v>0.511</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.018</v>
+        <v>0.757</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.169</v>
+        <v>0.26</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.343</v>
+        <v>0.197</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.698</v>
+        <v>2.167</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.186</v>
+        <v>0.167</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.034</v>
+        <v>0.022</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.142</v>
+        <v>0.141</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.104</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#6 D. GARCÍA (Per Game)</t>
+          <t>#6 K. ZORIKS (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C35" t="n">
-        <v>6.375</v>
+        <v>4.214</v>
       </c>
       <c r="D35" t="n">
-        <v>1.25</v>
+        <v>0.643</v>
       </c>
       <c r="E35" t="n">
-        <v>2.125</v>
+        <v>1.571</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0.571</v>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>2.143</v>
       </c>
       <c r="H35" t="n">
-        <v>0.875</v>
+        <v>1.214</v>
       </c>
       <c r="I35" t="n">
-        <v>0.875</v>
+        <v>1.857</v>
       </c>
       <c r="J35" t="n">
-        <v>4.5</v>
+        <v>1.643</v>
       </c>
       <c r="K35" t="n">
-        <v>2.75</v>
+        <v>0.714</v>
       </c>
       <c r="L35" t="n">
-        <v>0.625</v>
+        <v>0.143</v>
       </c>
       <c r="M35" t="n">
-        <v>1.125</v>
+        <v>0.5</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.75</v>
+        <v>1.071</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.75</v>
+        <v>1.071</v>
       </c>
       <c r="R35" t="n">
-        <v>3.875</v>
+        <v>1.786</v>
       </c>
       <c r="S35" t="n">
-        <v>1.875</v>
+        <v>1.786</v>
       </c>
       <c r="T35" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>0.643</v>
       </c>
       <c r="V35" t="n">
-        <v>1</v>
+        <v>0.143</v>
       </c>
       <c r="W35" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.125</v>
+        <v>1.571</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.25</v>
+        <v>2.357</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.9</v>
+        <v>0.667</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.125</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AC35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AG35" t="n">
         <v>0.375</v>
       </c>
-      <c r="AD35" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0.636</v>
-      </c>
       <c r="AH35" t="n">
-        <v>0.125</v>
+        <v>0.143</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.125</v>
+        <v>0.286</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.875</v>
+        <v>0.429</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.875</v>
+        <v>1.857</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.304</v>
+        <v>0.231</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>22:04</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>7.26</v>
+        <v>5.603</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.537</v>
+        <v>0.404</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.578</v>
+        <v>0.465</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.878</v>
+        <v>0.752</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.241</v>
+        <v>0.191</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.171</v>
+        <v>0.327</v>
       </c>
       <c r="AU35" t="n">
-        <v>2.571</v>
+        <v>1.533</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.151</v>
+        <v>0.197</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.032</v>
+        <v>0.012</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.139</v>
+        <v>0.061</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.173</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#6 K. ZORIKS (Per Game)</t>
+          <t>#7 G. GOLOMÁN (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C36" t="n">
-        <v>4.214</v>
+        <v>7.833</v>
       </c>
       <c r="D36" t="n">
-        <v>0.643</v>
+        <v>2.5</v>
       </c>
       <c r="E36" t="n">
-        <v>1.571</v>
+        <v>3.5</v>
       </c>
       <c r="F36" t="n">
-        <v>0.571</v>
+        <v>0.167</v>
       </c>
       <c r="G36" t="n">
-        <v>2.143</v>
+        <v>0.5</v>
       </c>
       <c r="H36" t="n">
-        <v>1.214</v>
+        <v>2.333</v>
       </c>
       <c r="I36" t="n">
-        <v>1.857</v>
+        <v>3.208</v>
       </c>
       <c r="J36" t="n">
-        <v>1.643</v>
+        <v>0.708</v>
       </c>
       <c r="K36" t="n">
-        <v>0.714</v>
+        <v>2.292</v>
       </c>
       <c r="L36" t="n">
-        <v>0.143</v>
+        <v>1.167</v>
       </c>
       <c r="M36" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T36" t="n">
+        <v>241</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="W36" t="n">
         <v>0.5</v>
       </c>
-      <c r="N36" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1.071</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1.071</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.786</v>
-      </c>
-      <c r="S36" t="n">
-        <v>1.786</v>
-      </c>
-      <c r="T36" t="n">
-        <v>48</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0.643</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.571</v>
+        <v>4.292</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.357</v>
+        <v>5.458</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.667</v>
+        <v>0.786</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.417</v>
       </c>
       <c r="AC36" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AL36" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD36" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1.857</v>
-      </c>
       <c r="AM36" t="n">
-        <v>0.231</v>
+        <v>0.333</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>5.603</v>
+        <v>6.328</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.404</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.465</v>
+        <v>0.724</v>
       </c>
       <c r="AR36" t="n">
-        <v>0.752</v>
+        <v>1.238</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.191</v>
+        <v>0.145</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.327</v>
+        <v>0.583</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.533</v>
+        <v>0.773</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.197</v>
+        <v>0.2</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.012</v>
+        <v>0.09</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.061</v>
+        <v>0.177</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.061</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#7 G. GOLOMÁN (Per Game)</t>
+          <t>#12 A. DIAGNE (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C37" t="n">
-        <v>8.318</v>
+        <v>5.968</v>
       </c>
       <c r="D37" t="n">
-        <v>2.682</v>
+        <v>2.419</v>
       </c>
       <c r="E37" t="n">
-        <v>3.727</v>
+        <v>3.161</v>
       </c>
       <c r="F37" t="n">
-        <v>0.182</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>2.409</v>
+        <v>1.129</v>
       </c>
       <c r="I37" t="n">
-        <v>3.318</v>
+        <v>1.71</v>
       </c>
       <c r="J37" t="n">
-        <v>0.773</v>
+        <v>0.29</v>
       </c>
       <c r="K37" t="n">
-        <v>2.455</v>
+        <v>1.677</v>
       </c>
       <c r="L37" t="n">
-        <v>1.273</v>
+        <v>1.484</v>
       </c>
       <c r="M37" t="n">
-        <v>0.455</v>
+        <v>0.258</v>
       </c>
       <c r="N37" t="n">
-        <v>0.591</v>
+        <v>1.032</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.955</v>
+        <v>0.871</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.955</v>
+        <v>0.871</v>
       </c>
       <c r="R37" t="n">
-        <v>2.318</v>
+        <v>2.774</v>
       </c>
       <c r="S37" t="n">
-        <v>2.545</v>
+        <v>1.323</v>
       </c>
       <c r="T37" t="n">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="U37" t="n">
-        <v>0.909</v>
+        <v>0.258</v>
       </c>
       <c r="V37" t="n">
-        <v>1.227</v>
+        <v>1.774</v>
       </c>
       <c r="W37" t="n">
-        <v>0.545</v>
+        <v>0.194</v>
       </c>
       <c r="X37" t="n">
-        <v>0.364</v>
+        <v>0.097</v>
       </c>
       <c r="Y37" t="n">
-        <v>4.5</v>
+        <v>3.194</v>
       </c>
       <c r="Z37" t="n">
-        <v>5.727</v>
+        <v>3.935</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.786</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.455</v>
+        <v>0.258</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.955</v>
+        <v>0.677</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.476</v>
+        <v>0.381</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.136</v>
+        <v>0.097</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.364</v>
+        <v>0.258</v>
       </c>
       <c r="AG37" t="n">
         <v>0.375</v>
@@ -6033,865 +6033,865 @@
         <v>0</v>
       </c>
       <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AO37" t="n">
+        <v>4.785</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.247</v>
+      </c>
+      <c r="AS37" t="n">
         <v>0.182</v>
       </c>
-      <c r="AL37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
-      <c r="AO37" t="n">
-        <v>6.642</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>0.699</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>0.731</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>1.252</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>0.144</v>
-      </c>
       <c r="AT37" t="n">
-        <v>0.57</v>
+        <v>0.357</v>
       </c>
       <c r="AU37" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.333</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.199</v>
+        <v>0.172</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.093</v>
+        <v>0.13</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.178</v>
+        <v>0.147</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.03</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#12 A. DIAGNE (Per Game)</t>
+          <t>#13 A. RODRIGUEZ (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="C38" t="n">
-        <v>5.593</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>2.259</v>
+        <v>0.875</v>
       </c>
       <c r="E38" t="n">
-        <v>3.074</v>
+        <v>1.75</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="H38" t="n">
-        <v>1.074</v>
+        <v>0.5</v>
       </c>
       <c r="I38" t="n">
-        <v>1.444</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>0.259</v>
+        <v>1.375</v>
       </c>
       <c r="K38" t="n">
-        <v>1.519</v>
+        <v>0.75</v>
       </c>
       <c r="L38" t="n">
-        <v>1.519</v>
+        <v>0.625</v>
       </c>
       <c r="M38" t="n">
-        <v>0.259</v>
+        <v>0.625</v>
       </c>
       <c r="N38" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S38" t="n">
         <v>1</v>
       </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1</v>
-      </c>
-      <c r="R38" t="n">
-        <v>2.741</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1.222</v>
-      </c>
       <c r="T38" t="n">
-        <v>174</v>
+        <v>29</v>
       </c>
       <c r="U38" t="n">
-        <v>0.296</v>
+        <v>0.5</v>
       </c>
       <c r="V38" t="n">
-        <v>1.778</v>
+        <v>0.375</v>
       </c>
       <c r="W38" t="n">
-        <v>0.222</v>
+        <v>0.375</v>
       </c>
       <c r="X38" t="n">
-        <v>0.111</v>
+        <v>0.375</v>
       </c>
       <c r="Y38" t="n">
-        <v>3</v>
+        <v>1.375</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.519</v>
+        <v>2.25</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.853</v>
+        <v>0.611</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.259</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.741</v>
+        <v>0.125</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.074</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.259</v>
+        <v>0.375</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
         <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AJ38" t="n">
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>4.71</v>
+        <v>3.69</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.735</v>
+        <v>0.476</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.754</v>
+        <v>0.489</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.187</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.212</v>
+        <v>0.169</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.349</v>
+        <v>0.19</v>
       </c>
       <c r="AU38" t="n">
-        <v>0.259</v>
+        <v>2.2</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.171</v>
+        <v>0.19</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.135</v>
+        <v>0.078</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.134</v>
+        <v>0.094</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#13 A. RODRIGUEZ (Per Game)</t>
+          <t>#14 M. SANZ (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C39" t="n">
-        <v>3.25</v>
+        <v>4.812</v>
       </c>
       <c r="D39" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.812</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.812</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="I39" t="n">
         <v>0.75</v>
       </c>
-      <c r="E39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="F39" t="n">
+      <c r="J39" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1.219</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="T39" t="n">
+        <v>131</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="W39" t="n">
         <v>0.25</v>
       </c>
-      <c r="G39" t="n">
+      <c r="X39" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.469</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.156</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="AI39" t="n">
         <v>0.75</v>
       </c>
-      <c r="H39" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" t="n">
-        <v>2</v>
-      </c>
-      <c r="J39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R39" t="n">
-        <v>2</v>
-      </c>
-      <c r="S39" t="n">
-        <v>1</v>
-      </c>
-      <c r="T39" t="n">
-        <v>14</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0.25</v>
-      </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>0.292</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.25</v>
+        <v>0.406</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.5</v>
+        <v>1.062</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.5</v>
+        <v>0.382</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>3.38</v>
+        <v>4.361</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.612</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.608</v>
       </c>
       <c r="AR39" t="n">
-        <v>0.962</v>
+        <v>1.103</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.148</v>
+        <v>0.093</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.5</v>
+        <v>0.103</v>
       </c>
       <c r="AU39" t="n">
-        <v>3</v>
+        <v>1.308</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.173</v>
+        <v>0.143</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.093</v>
+        <v>0.098</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.055</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#14 M. SANZ (Per Game)</t>
+          <t>#16 M. JIMÉNEZ (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C40" t="n">
-        <v>4.571</v>
+        <v>4.4</v>
       </c>
       <c r="D40" t="n">
-        <v>1.143</v>
+        <v>1.033</v>
       </c>
       <c r="E40" t="n">
-        <v>1.679</v>
+        <v>1.767</v>
       </c>
       <c r="F40" t="n">
-        <v>0.643</v>
+        <v>0.633</v>
       </c>
       <c r="G40" t="n">
-        <v>1.857</v>
+        <v>2.133</v>
       </c>
       <c r="H40" t="n">
-        <v>0.357</v>
+        <v>0.433</v>
       </c>
       <c r="I40" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
-        <v>0.571</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>1.321</v>
+        <v>1.733</v>
       </c>
       <c r="L40" t="n">
-        <v>0.643</v>
+        <v>0.533</v>
       </c>
       <c r="M40" t="n">
-        <v>0.393</v>
+        <v>0.4</v>
       </c>
       <c r="N40" t="n">
-        <v>0.321</v>
+        <v>0.267</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.429</v>
+        <v>1.067</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.429</v>
+        <v>1.067</v>
       </c>
       <c r="R40" t="n">
-        <v>1.857</v>
+        <v>1</v>
       </c>
       <c r="S40" t="n">
-        <v>0.536</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="T40" t="n">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="U40" t="n">
-        <v>0.893</v>
+        <v>0.7</v>
       </c>
       <c r="V40" t="n">
-        <v>0.786</v>
+        <v>0.2</v>
       </c>
       <c r="W40" t="n">
-        <v>0.179</v>
+        <v>0.8</v>
       </c>
       <c r="X40" t="n">
-        <v>0.107</v>
+        <v>0.4</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.286</v>
+        <v>1.033</v>
       </c>
       <c r="Z40" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.643</v>
+        <v>0.738</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.143</v>
+        <v>0.233</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.25</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.571</v>
+        <v>0.412</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.179</v>
+        <v>0.5</v>
       </c>
       <c r="AG40" t="n">
         <v>0.4</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.786</v>
+        <v>0.767</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.318</v>
+        <v>0.391</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.393</v>
+        <v>0.333</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.071</v>
+        <v>1.367</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.367</v>
+        <v>0.244</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>4.294</v>
+        <v>5.275</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.596</v>
+        <v>0.509</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.591</v>
+        <v>0.523</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.065</v>
+        <v>0.834</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.1</v>
+        <v>0.202</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.101</v>
+        <v>0.111</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.333</v>
+        <v>0.875</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.138</v>
+        <v>0.202</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.051</v>
+        <v>0.05</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.103</v>
+        <v>0.162</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.022</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>#16 M. JIMÉNEZ (Per Game)</t>
+          <t>#22 J. SHURNA (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>5.643</v>
       </c>
       <c r="D41" t="n">
-        <v>0.846</v>
+        <v>0.714</v>
       </c>
       <c r="E41" t="n">
-        <v>1.538</v>
+        <v>1.429</v>
       </c>
       <c r="F41" t="n">
-        <v>0.615</v>
+        <v>1.214</v>
       </c>
       <c r="G41" t="n">
-        <v>2.077</v>
+        <v>3.179</v>
       </c>
       <c r="H41" t="n">
-        <v>0.462</v>
+        <v>0.571</v>
       </c>
       <c r="I41" t="n">
-        <v>0.731</v>
+        <v>0.75</v>
       </c>
       <c r="J41" t="n">
-        <v>0.846</v>
+        <v>0.571</v>
       </c>
       <c r="K41" t="n">
-        <v>1.808</v>
+        <v>2.25</v>
       </c>
       <c r="L41" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="M41" t="n">
-        <v>0.462</v>
+        <v>0.286</v>
       </c>
       <c r="N41" t="n">
-        <v>0.308</v>
+        <v>0.571</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.077</v>
+        <v>0.286</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.077</v>
+        <v>0.286</v>
       </c>
       <c r="R41" t="n">
-        <v>0.923</v>
+        <v>1.143</v>
       </c>
       <c r="S41" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="T41" t="n">
+        <v>175</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="Y41" t="n">
         <v>1</v>
       </c>
-      <c r="T41" t="n">
-        <v>117</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0.577</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0.731</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>0.962</v>
-      </c>
       <c r="Z41" t="n">
-        <v>1.346</v>
+        <v>1.25</v>
       </c>
       <c r="AA41" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AF41" t="n">
         <v>0.714</v>
       </c>
-      <c r="AB41" t="n">
-        <v>0.192</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>0.423</v>
-      </c>
       <c r="AG41" t="n">
-        <v>0.364</v>
+        <v>0.35</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.308</v>
+        <v>0.536</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.731</v>
+        <v>1.179</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.421</v>
+        <v>0.455</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.308</v>
+        <v>0.679</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.346</v>
+        <v>2</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.229</v>
+        <v>0.339</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>5.014</v>
+        <v>5.223</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.489</v>
+        <v>0.55</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.508</v>
+        <v>0.571</v>
       </c>
       <c r="AR41" t="n">
-        <v>0.798</v>
+        <v>1.08</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.215</v>
+        <v>0.055</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.128</v>
+        <v>0.124</v>
       </c>
       <c r="AU41" t="n">
-        <v>0.786</v>
+        <v>2</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.191</v>
+        <v>0.137</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.047</v>
+        <v>0.036</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.168</v>
+        <v>0.144</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.032</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>#22 J. SHURNA (Per Game)</t>
+          <t>#25 C. KRUTWIG (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C42" t="n">
-        <v>5.852</v>
+        <v>4.812</v>
       </c>
       <c r="D42" t="n">
-        <v>0.741</v>
+        <v>1.906</v>
       </c>
       <c r="E42" t="n">
-        <v>1.481</v>
+        <v>3.719</v>
       </c>
       <c r="F42" t="n">
-        <v>1.259</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>3.259</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.593</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>0.778</v>
+        <v>1.406</v>
       </c>
       <c r="J42" t="n">
-        <v>0.593</v>
+        <v>1.594</v>
       </c>
       <c r="K42" t="n">
-        <v>2.333</v>
+        <v>1.719</v>
       </c>
       <c r="L42" t="n">
-        <v>0.593</v>
+        <v>1.062</v>
       </c>
       <c r="M42" t="n">
-        <v>0.296</v>
+        <v>0.406</v>
       </c>
       <c r="N42" t="n">
-        <v>0.593</v>
+        <v>0.594</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0.296</v>
+        <v>0.75</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.296</v>
+        <v>0.75</v>
       </c>
       <c r="R42" t="n">
-        <v>1.185</v>
+        <v>1.281</v>
       </c>
       <c r="S42" t="n">
-        <v>0.667</v>
+        <v>1.281</v>
       </c>
       <c r="T42" t="n">
-        <v>176</v>
+        <v>231</v>
       </c>
       <c r="U42" t="n">
-        <v>0.667</v>
+        <v>0.188</v>
       </c>
       <c r="V42" t="n">
-        <v>0.444</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="W42" t="n">
-        <v>0.407</v>
+        <v>0.188</v>
       </c>
       <c r="X42" t="n">
-        <v>0.148</v>
+        <v>0.125</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.037</v>
+        <v>2.219</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.296</v>
+        <v>3.062</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.8</v>
+        <v>0.724</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.037</v>
+        <v>0.438</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.222</v>
+        <v>1.312</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.167</v>
+        <v>0.333</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.259</v>
+        <v>0.25</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.741</v>
+        <v>0.75</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.35</v>
+        <v>0.333</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.185</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.469</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.704</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>2.074</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.339</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>5.379</v>
+        <v>5.087</v>
       </c>
       <c r="AP42" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="AQ42" t="n">
         <v>0.555</v>
       </c>
-      <c r="AQ42" t="n">
-        <v>0.576</v>
-      </c>
       <c r="AR42" t="n">
-        <v>1.088</v>
+        <v>0.946</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.055</v>
+        <v>0.147</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.125</v>
+        <v>0.269</v>
       </c>
       <c r="AU42" t="n">
-        <v>2</v>
+        <v>2.125</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.139</v>
+        <v>0.162</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.038</v>
+        <v>0.082</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.147</v>
+        <v>0.134</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.023</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>#25 C. KRUTWIG (Per Game)</t>
+          <t>#50 P. RIOS (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="C43" t="n">
-        <v>3.786</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>1.393</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>3.179</v>
+        <v>0.5</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -6900,316 +6900,316 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>1.429</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="K43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1.036</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.357</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0.536</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0.643</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.643</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>1.286</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>165</v>
+        <v>-1</v>
       </c>
       <c r="U43" t="n">
-        <v>0.214</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0.643</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0.107</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.893</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.786</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.679</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.393</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.321</v>
+        <v>0.25</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.297</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.107</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN43" t="inlineStr">
+        <is>
+          <t>00:34</t>
+        </is>
+      </c>
+      <c r="AO43" t="n">
         <v>0.5</v>
       </c>
-      <c r="AG43" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AO43" t="n">
-        <v>4.45</v>
-      </c>
       <c r="AP43" t="n">
-        <v>0.438</v>
+        <v>0</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.497</v>
+        <v>0</v>
       </c>
       <c r="AR43" t="n">
-        <v>0.851</v>
+        <v>0</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.144</v>
+        <v>0</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
       <c r="AU43" t="n">
-        <v>2.333</v>
+        <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.156</v>
+        <v>0.406</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.089</v>
+        <v>0</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.128</v>
+        <v>0</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.056</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>#50 P. RIOS (Per Game)</t>
+          <t>#52 I. DABO (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
+        <v>7</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="T44" t="n">
         <v>4</v>
       </c>
-      <c r="C44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN44" t="inlineStr">
+        <is>
+          <t>01:42</t>
+        </is>
+      </c>
+      <c r="AO44" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS44" t="n">
         <v>0.25</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>00:34</t>
-        </is>
-      </c>
-      <c r="AO44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>0</v>
-      </c>
       <c r="AT44" t="n">
         <v>0</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.406</v>
+        <v>0.153</v>
       </c>
       <c r="AW44" t="n">
         <v>0</v>
       </c>
       <c r="AX44" t="n">
-        <v>0</v>
+        <v>0.187</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>#52 I. DABO (Per Game)</t>
+          <t>#55 P. TORRENS (Per Game)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -7224,10 +7224,10 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -7236,25 +7236,25 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.143</v>
+        <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.143</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>0.429</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -7269,13 +7269,13 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
         <v>0</v>
@@ -7315,51 +7315,51 @@
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>01:42</t>
+          <t>02:20</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>0.571</v>
+        <v>1</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AR45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS45" t="n">
         <v>1</v>
       </c>
-      <c r="AS45" t="n">
-        <v>0.25</v>
-      </c>
       <c r="AT45" t="n">
         <v>0</v>
       </c>
       <c r="AU45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.153</v>
+        <v>0.197</v>
       </c>
       <c r="AW45" t="n">
         <v>0</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.186</v>
+        <v>0</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>#55 P. TORRENS (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -7386,10 +7386,10 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1.844</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -7401,19 +7401,19 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1</v>
+        <v>0.844</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1</v>
+        <v>0.469</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -7474,11 +7474,11 @@
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>02:20</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP46" t="n">
         <v>0</v>
@@ -7490,7 +7490,7 @@
         <v>0</v>
       </c>
       <c r="AS46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT46" t="n">
         <v>0</v>
@@ -7499,7 +7499,7 @@
         <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>0.197</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
         <v>0</v>
@@ -7514,157 +7514,157 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>83.53100000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>21.188</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>38.844</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>7.688</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>24.094</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>18.094</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>23.812</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>17.062</v>
       </c>
       <c r="K47" t="n">
-        <v>1.75</v>
+        <v>25.375</v>
       </c>
       <c r="L47" t="n">
-        <v>1.214</v>
+        <v>10.438</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>6.656</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>6.281</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0.964</v>
+        <v>13.562</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>12.719</v>
       </c>
       <c r="R47" t="n">
-        <v>0.536</v>
+        <v>24.281</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>22.094</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3002</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>10.719</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>10.219</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>3.406</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>32.438</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>43.312</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>0.749</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>3.812</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>10.094</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>0.378</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>3.031</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>0.328</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>2.188</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>5.812</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>0.376</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>18.281</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>0.301</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>200:00</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>0</v>
+        <v>86.977</v>
       </c>
       <c r="AP47" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0</v>
+        <v>0.569</v>
       </c>
       <c r="AR47" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AS47" t="n">
-        <v>0</v>
+        <v>0.156</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>0.287</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>1.258</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>0.142</v>
       </c>
       <c r="AY47" t="n">
         <v>0</v>
@@ -7673,477 +7673,159 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>89.53100000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>18.781</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>34.469</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>10.688</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>29.781</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>19.906</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>25.594</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>17.25</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>25.312</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>10.281</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>7.188</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>6.281</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>12.062</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>11.188</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>22.344</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>23.75</v>
       </c>
       <c r="T48" t="n">
-        <v>41</v>
+        <v>3351</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>10.875</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>10.531</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>5.125</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>3.156</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>31.656</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>0.782</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>9.531000000000001</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>0.367</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>3.531</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>10.031</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>0.352</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>3.094</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>7.625</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>0.406</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>7.594</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>22.156</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>0.343</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>200:00</t>
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>0.964</v>
+        <v>87.574</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>0.542</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>0.593</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>1.022</v>
       </c>
       <c r="AS48" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="AU48" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>0.201</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="AX48" t="n">
-        <v>0</v>
+        <v>0.142</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>28</v>
-      </c>
-      <c r="C49" t="n">
-        <v>83.214</v>
-      </c>
-      <c r="D49" t="n">
-        <v>20.321</v>
-      </c>
-      <c r="E49" t="n">
-        <v>37.964</v>
-      </c>
-      <c r="F49" t="n">
-        <v>7.929</v>
-      </c>
-      <c r="G49" t="n">
-        <v>24.393</v>
-      </c>
-      <c r="H49" t="n">
-        <v>18.786</v>
-      </c>
-      <c r="I49" t="n">
-        <v>24.321</v>
-      </c>
-      <c r="J49" t="n">
-        <v>16.821</v>
-      </c>
-      <c r="K49" t="n">
-        <v>25.25</v>
-      </c>
-      <c r="L49" t="n">
-        <v>10.429</v>
-      </c>
-      <c r="M49" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="N49" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>13.821</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>12.857</v>
-      </c>
-      <c r="R49" t="n">
-        <v>24.607</v>
-      </c>
-      <c r="S49" t="n">
-        <v>22.357</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2611</v>
-      </c>
-      <c r="U49" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="V49" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="W49" t="n">
-        <v>5.393</v>
-      </c>
-      <c r="X49" t="n">
-        <v>3.357</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>32.286</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>42.857</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0.753</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>10.429</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0.384</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>2.821</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0.313</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>2.321</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>5.821</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0.399</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>5.607</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>18.571</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>0.302</v>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO49" t="n">
-        <v>86.88</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>0.517</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>0.958</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>0.301</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>1.217</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>28</v>
-      </c>
-      <c r="C50" t="n">
-        <v>89.25</v>
-      </c>
-      <c r="D50" t="n">
-        <v>18.821</v>
-      </c>
-      <c r="E50" t="n">
-        <v>34.393</v>
-      </c>
-      <c r="F50" t="n">
-        <v>10.536</v>
-      </c>
-      <c r="G50" t="n">
-        <v>29.857</v>
-      </c>
-      <c r="H50" t="n">
-        <v>20</v>
-      </c>
-      <c r="I50" t="n">
-        <v>25.786</v>
-      </c>
-      <c r="J50" t="n">
-        <v>17.214</v>
-      </c>
-      <c r="K50" t="n">
-        <v>25</v>
-      </c>
-      <c r="L50" t="n">
-        <v>10.536</v>
-      </c>
-      <c r="M50" t="n">
-        <v>7.214</v>
-      </c>
-      <c r="N50" t="n">
-        <v>6.571</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>12.036</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>11.107</v>
-      </c>
-      <c r="R50" t="n">
-        <v>22.679</v>
-      </c>
-      <c r="S50" t="n">
-        <v>24</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2923</v>
-      </c>
-      <c r="U50" t="n">
-        <v>10.536</v>
-      </c>
-      <c r="V50" t="n">
-        <v>10.571</v>
-      </c>
-      <c r="W50" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="X50" t="n">
-        <v>3.393</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>40.286</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0.782</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>3.821</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>10.036</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0.381</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>9.856999999999999</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>3.214</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>7.821</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>7.321</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>22.036</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>0.332</v>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO50" t="n">
-        <v>87.631</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>0.539</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>1.018</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>0.311</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>0.202</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AY50" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Hiopos Lleida.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Hiopos Lleida.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2449.28</v>
+        <v>2612.92</v>
       </c>
       <c r="C2" t="n">
-        <v>2461.320000000001</v>
+        <v>2624.920000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>108.6002632733655</v>
+        <v>108.8033159105801</v>
       </c>
       <c r="E2" t="n">
-        <v>116.4009555848081</v>
+        <v>117.9845481005135</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5198609731876862</v>
+        <v>0.52143522833178</v>
       </c>
       <c r="G2" t="n">
-        <v>0.155931131614498</v>
+        <v>0.1568009906053999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.291958041958042</v>
+        <v>0.2942622950819672</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2874875868917577</v>
+        <v>0.287977632805219</v>
       </c>
       <c r="J2" t="n">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="K2" t="n">
-        <v>327</v>
+        <v>361</v>
       </c>
       <c r="L2" t="n">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="M2" t="n">
-        <v>407</v>
+        <v>438</v>
       </c>
       <c r="N2" t="n">
-        <v>1038</v>
+        <v>1113</v>
       </c>
       <c r="O2" t="n">
-        <v>1386</v>
+        <v>1496</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6881827209533267</v>
+        <v>0.6971109040074557</v>
       </c>
       <c r="Q2" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="R2" t="n">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="S2" t="n">
-        <v>0.160377358490566</v>
+        <v>0.1570363466915191</v>
       </c>
       <c r="T2" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="U2" t="n">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1469712015888779</v>
+        <v>0.1463187325256291</v>
       </c>
       <c r="W2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="X2" t="n">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09235352532274081</v>
+        <v>0.09226467847157502</v>
       </c>
       <c r="Z2" t="n">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="AA2" t="n">
-        <v>585</v>
+        <v>619</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2904667328699106</v>
+        <v>0.2884436160298229</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7489177489177489</v>
+        <v>0.7439839572192514</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.3777089783281734</v>
+        <v>0.3768545994065282</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3277027027027027</v>
+        <v>0.321656050955414</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3763440860215054</v>
+        <v>0.3787878787878788</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3008547008547008</v>
+        <v>0.3053311793214863</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.497835497835498</v>
+        <v>1.487967914438503</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.6554054054054054</v>
+        <v>0.643312101910828</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.9571984435797666</v>
+        <v>0.9694002447980417</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.8886010362694301</v>
+        <v>0.8948655256723717</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.9790419161676647</v>
+        <v>1.005571030640668</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.614678899082569</v>
+        <v>1.598290598290598</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.258064516129032</v>
+        <v>1.251072961373391</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.640552995391705</v>
+        <v>4.605150214592275</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.898617511520738</v>
+        <v>5.856223175965665</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>76.54000000000001</v>
+        <v>76.85058823529413</v>
       </c>
       <c r="C3" t="n">
-        <v>76.91625000000002</v>
+        <v>77.20352941176472</v>
       </c>
       <c r="D3" t="n">
-        <v>108.6002632733655</v>
+        <v>108.8033159105801</v>
       </c>
       <c r="E3" t="n">
-        <v>116.4009555848081</v>
+        <v>117.9845481005135</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5198609731876862</v>
+        <v>0.5214352283317801</v>
       </c>
       <c r="G3" t="n">
-        <v>0.155931131614498</v>
+        <v>0.1568009906053999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.291958041958042</v>
+        <v>0.2942622950819672</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2874875868917577</v>
+        <v>0.287977632805219</v>
       </c>
       <c r="J3" t="n">
-        <v>10.71875</v>
+        <v>10.76470588235294</v>
       </c>
       <c r="K3" t="n">
-        <v>10.21875</v>
+        <v>10.61764705882353</v>
       </c>
       <c r="L3" t="n">
         <v>5.5</v>
       </c>
       <c r="M3" t="n">
-        <v>12.71875</v>
+        <v>12.88235294117647</v>
       </c>
       <c r="N3" t="n">
-        <v>32.4375</v>
+        <v>32.73529411764706</v>
       </c>
       <c r="O3" t="n">
-        <v>43.3125</v>
+        <v>44</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6881827209533267</v>
+        <v>0.6971109040074558</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.8125</v>
+        <v>3.735294117647059</v>
       </c>
       <c r="R3" t="n">
-        <v>10.09375</v>
+        <v>9.911764705882353</v>
       </c>
       <c r="S3" t="n">
-        <v>0.160377358490566</v>
+        <v>0.1570363466915191</v>
       </c>
       <c r="T3" t="n">
-        <v>3.03125</v>
+        <v>2.970588235294118</v>
       </c>
       <c r="U3" t="n">
-        <v>9.25</v>
+        <v>9.235294117647058</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1469712015888779</v>
+        <v>0.1463187325256291</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1875</v>
+        <v>2.205882352941177</v>
       </c>
       <c r="X3" t="n">
-        <v>5.8125</v>
+        <v>5.823529411764706</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.09235352532274081</v>
+        <v>0.09226467847157502</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.5</v>
+        <v>5.558823529411764</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.28125</v>
+        <v>18.20588235294118</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2904667328699106</v>
+        <v>0.2884436160298229</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7489177489177489</v>
+        <v>0.7439839572192514</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.3777089783281734</v>
+        <v>0.3768545994065282</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3277027027027027</v>
+        <v>0.3216560509554141</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3763440860215054</v>
+        <v>0.3787878787878788</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3008547008547008</v>
+        <v>0.3053311793214862</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.497835497835498</v>
+        <v>1.487967914438503</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.6554054054054054</v>
+        <v>0.6433121019108281</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.9571984435797666</v>
+        <v>0.9694002447980415</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8886010362694301</v>
+        <v>0.8948655256723718</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.9790419161676647</v>
+        <v>1.005571030640668</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.614678899082569</v>
+        <v>1.598290598290598</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.258064516129032</v>
+        <v>1.251072961373391</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.640552995391705</v>
+        <v>4.605150214592275</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.898617511520738</v>
+        <v>5.856223175965666</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2473.359999999999</v>
+        <v>2636.92</v>
       </c>
       <c r="C4" t="n">
-        <v>2461.320000000001</v>
+        <v>2624.920000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>116.4009555848081</v>
+        <v>117.9845481005135</v>
       </c>
       <c r="E4" t="n">
-        <v>108.6002632733655</v>
+        <v>108.8033159105801</v>
       </c>
       <c r="F4" t="n">
-        <v>0.541828793774319</v>
+        <v>0.5487528344671202</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1377410468319559</v>
+        <v>0.1365189991722075</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2883435582822086</v>
+        <v>0.29644921552436</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3098249027237354</v>
+        <v>0.3070294784580499</v>
       </c>
       <c r="J4" t="n">
-        <v>348</v>
+        <v>378</v>
       </c>
       <c r="K4" t="n">
-        <v>337</v>
+        <v>381</v>
       </c>
       <c r="L4" t="n">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="M4" t="n">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="N4" t="n">
-        <v>1013</v>
+        <v>1089</v>
       </c>
       <c r="O4" t="n">
-        <v>1296</v>
+        <v>1392</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6303501945525292</v>
+        <v>0.6312925170068027</v>
       </c>
       <c r="Q4" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="R4" t="n">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1483463035019455</v>
+        <v>0.1442176870748299</v>
       </c>
       <c r="T4" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="U4" t="n">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1561284046692607</v>
+        <v>0.1551020408163265</v>
       </c>
       <c r="W4" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="X4" t="n">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1186770428015564</v>
+        <v>0.1183673469387755</v>
       </c>
       <c r="Z4" t="n">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="AA4" t="n">
-        <v>709</v>
+        <v>760</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3448443579766537</v>
+        <v>0.344671201814059</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7816358024691358</v>
+        <v>0.7823275862068966</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.3672131147540983</v>
+        <v>0.3647798742138365</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.35202492211838</v>
+        <v>0.3625730994152047</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4057377049180328</v>
+        <v>0.4061302681992337</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3427362482369535</v>
+        <v>0.35</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.563271604938272</v>
+        <v>1.564655172413793</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.7040498442367601</v>
+        <v>0.7251461988304093</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.076600209863589</v>
+        <v>1.093046033300686</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8018433179723502</v>
+        <v>0.8111587982832618</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.024316109422492</v>
+        <v>1.061281337047354</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.623762376237624</v>
+        <v>1.572649572649573</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.430051813471503</v>
+        <v>1.432762836185819</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.326424870466322</v>
+        <v>5.39119804400978</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.756476683937824</v>
+        <v>6.823960880195599</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>77.29249999999998</v>
+        <v>77.55647058823529</v>
       </c>
       <c r="C5" t="n">
-        <v>76.91625000000002</v>
+        <v>77.20352941176472</v>
       </c>
       <c r="D5" t="n">
-        <v>116.4009555848081</v>
+        <v>117.9845481005135</v>
       </c>
       <c r="E5" t="n">
-        <v>108.6002632733655</v>
+        <v>108.8033159105801</v>
       </c>
       <c r="F5" t="n">
-        <v>0.541828793774319</v>
+        <v>0.5487528344671203</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1377410468319559</v>
+        <v>0.1365189991722076</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2883435582822086</v>
+        <v>0.29644921552436</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3098249027237354</v>
+        <v>0.3070294784580499</v>
       </c>
       <c r="J5" t="n">
-        <v>10.875</v>
+        <v>11.11764705882353</v>
       </c>
       <c r="K5" t="n">
-        <v>10.53125</v>
+        <v>11.20588235294118</v>
       </c>
       <c r="L5" t="n">
-        <v>5.125</v>
+        <v>5.411764705882353</v>
       </c>
       <c r="M5" t="n">
-        <v>11.1875</v>
+        <v>11.17647058823529</v>
       </c>
       <c r="N5" t="n">
-        <v>31.65625</v>
+        <v>32.02941176470588</v>
       </c>
       <c r="O5" t="n">
-        <v>40.5</v>
+        <v>40.94117647058823</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6303501945525292</v>
+        <v>0.6312925170068028</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.5</v>
+        <v>3.411764705882353</v>
       </c>
       <c r="R5" t="n">
-        <v>9.53125</v>
+        <v>9.352941176470589</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1483463035019455</v>
+        <v>0.14421768707483</v>
       </c>
       <c r="T5" t="n">
-        <v>3.53125</v>
+        <v>3.647058823529412</v>
       </c>
       <c r="U5" t="n">
-        <v>10.03125</v>
+        <v>10.05882352941176</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1561284046692607</v>
+        <v>0.1551020408163266</v>
       </c>
       <c r="W5" t="n">
-        <v>3.09375</v>
+        <v>3.117647058823529</v>
       </c>
       <c r="X5" t="n">
-        <v>7.625</v>
+        <v>7.676470588235294</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1186770428015564</v>
+        <v>0.1183673469387755</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.59375</v>
+        <v>7.823529411764706</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.15625</v>
+        <v>22.35294117647059</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3448443579766537</v>
+        <v>0.344671201814059</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7816358024691358</v>
+        <v>0.7823275862068967</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.3672131147540983</v>
+        <v>0.3647798742138365</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.35202492211838</v>
+        <v>0.3625730994152047</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4057377049180328</v>
+        <v>0.4061302681992337</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3427362482369535</v>
+        <v>0.35</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.563271604938272</v>
+        <v>1.564655172413793</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.7040498442367601</v>
+        <v>0.7251461988304093</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.076600209863589</v>
+        <v>1.093046033300686</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8018433179723502</v>
+        <v>0.8111587982832618</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.024316109422492</v>
+        <v>1.061281337047354</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.623762376237624</v>
+        <v>1.572649572649573</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.430051813471503</v>
+        <v>1.432762836185819</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.326424870466322</v>
+        <v>5.391198044009779</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.756476683937824</v>
+        <v>6.823960880195599</v>
       </c>
     </row>
     <row r="7">
@@ -1419,31 +1419,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C8" t="n">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c r="D8" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E8" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="F8" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G8" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="H8" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I8" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="J8" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K8" t="n">
         <v>44</v>
@@ -1452,7 +1452,7 @@
         <v>26</v>
       </c>
       <c r="M8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N8" t="n">
         <v>23</v>
@@ -1461,19 +1461,19 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="Q8" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="R8" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="S8" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="T8" t="n">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="U8" t="n">
         <v>74</v>
@@ -1488,87 +1488,87 @@
         <v>29</v>
       </c>
       <c r="Y8" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Z8" t="n">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.799</v>
       </c>
       <c r="AB8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC8" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.442</v>
+        <v>0.444</v>
       </c>
       <c r="AE8" t="n">
         <v>13</v>
       </c>
       <c r="AF8" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.333</v>
+        <v>0.317</v>
       </c>
       <c r="AH8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.323</v>
+        <v>0.344</v>
       </c>
       <c r="AK8" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AL8" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.331</v>
+        <v>0.326</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>796:29</t>
+          <t>832:36</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>449.72</v>
+        <v>472.6</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.491</v>
+        <v>0.486</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.597</v>
+        <v>0.589</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.061</v>
+        <v>1.039</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.111</v>
+        <v>0.118</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.524</v>
+        <v>0.502</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.74</v>
+        <v>1.625</v>
       </c>
       <c r="AV8" t="n">
         <v>0.26</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.037</v>
+        <v>0.035</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.11</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="9">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" t="n">
         <v>124</v>
@@ -1587,13 +1587,13 @@
         <v>25</v>
       </c>
       <c r="E9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F9" t="n">
         <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H9" t="n">
         <v>29</v>
@@ -1602,10 +1602,10 @@
         <v>36</v>
       </c>
       <c r="J9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K9" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L9" t="n">
         <v>9</v>
@@ -1614,25 +1614,25 @@
         <v>21</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="S9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T9" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="U9" t="n">
         <v>21</v>
@@ -1668,10 +1668,10 @@
         <v>3</v>
       </c>
       <c r="AF9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.214</v>
+        <v>0.2</v>
       </c>
       <c r="AH9" t="n">
         <v>9</v>
@@ -1686,48 +1686,48 @@
         <v>6</v>
       </c>
       <c r="AL9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.115</v>
+        <v>0.113</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>540:07</t>
+          <t>550:43</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>172.84</v>
+        <v>175.84</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.393</v>
+        <v>0.386</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.453</v>
+        <v>0.447</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.717</v>
+        <v>0.705</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.208</v>
+        <v>0.21</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.24</v>
+        <v>0.236</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.361</v>
+        <v>1.351</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.147</v>
+        <v>0.146</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.104</v>
+        <v>0.108</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.055</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="10">
@@ -1737,37 +1737,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="D10" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E10" t="n">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F10" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H10" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I10" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="J10" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K10" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="L10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M10" t="n">
         <v>24</v>
@@ -1779,25 +1779,25 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q10" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R10" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="S10" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="T10" t="n">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="U10" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="V10" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="W10" t="n">
         <v>28</v>
@@ -1806,31 +1806,31 @@
         <v>17</v>
       </c>
       <c r="Y10" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="Z10" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="AB10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AC10" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.444</v>
+        <v>0.455</v>
       </c>
       <c r="AE10" t="n">
         <v>14</v>
       </c>
       <c r="AF10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.298</v>
+        <v>0.292</v>
       </c>
       <c r="AH10" t="n">
         <v>5</v>
@@ -1842,48 +1842,48 @@
         <v>0.278</v>
       </c>
       <c r="AK10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL10" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.394</v>
+        <v>0.397</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>784:24</t>
+          <t>819:52</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>367.92</v>
+        <v>380.44</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.536</v>
+        <v>0.537</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.591</v>
+        <v>0.594</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.027</v>
+        <v>1.036</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.13</v>
+        <v>0.129</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.283</v>
+        <v>0.3</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.667</v>
+        <v>0.714</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.216</v>
+        <v>0.212</v>
       </c>
       <c r="AW10" t="n">
         <v>0.06</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.183</v>
+        <v>0.179</v>
       </c>
       <c r="AY10" t="n">
         <v>0.041</v>
@@ -1896,40 +1896,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C11" t="n">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="D11" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E11" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="F11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G11" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H11" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I11" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J11" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="K11" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M11" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N11" t="n">
         <v>18</v>
@@ -1938,19 +1938,19 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R11" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="S11" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T11" t="n">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="U11" t="n">
         <v>37</v>
@@ -1965,84 +1965,84 @@
         <v>2</v>
       </c>
       <c r="Y11" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Z11" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.606</v>
+        <v>0.607</v>
       </c>
       <c r="AB11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC11" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.269</v>
+        <v>0.283</v>
       </c>
       <c r="AE11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AF11" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.317</v>
+        <v>0.328</v>
       </c>
       <c r="AH11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="AK11" t="n">
         <v>21</v>
       </c>
       <c r="AL11" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.266</v>
+        <v>0.259</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>532:00</t>
+          <t>560:06</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>343.72</v>
+        <v>354.6</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.4</v>
+        <v>0.404</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.432</v>
+        <v>0.436</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.739</v>
+        <v>0.747</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.145</v>
+        <v>0.144</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.154</v>
+        <v>0.156</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.3</v>
+        <v>1.353</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.297</v>
+        <v>0.29</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.057</v>
+        <v>0.058</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.133</v>
+        <v>0.128</v>
       </c>
       <c r="AY11" t="n">
         <v>0.078</v>
@@ -2055,79 +2055,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>312</v>
+        <v>343</v>
       </c>
       <c r="D12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E12" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G12" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="H12" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="I12" t="n">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="J12" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="K12" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="L12" t="n">
         <v>20</v>
       </c>
       <c r="M12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="Q12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="R12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="S12" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="T12" t="n">
-        <v>408</v>
+        <v>454</v>
       </c>
       <c r="U12" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="V12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="W12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y12" t="n">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="Z12" t="n">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="AA12" t="n">
         <v>0.746</v>
@@ -2136,75 +2136,75 @@
         <v>10</v>
       </c>
       <c r="AC12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.435</v>
+        <v>0.417</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
       </c>
       <c r="AF12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.259</v>
+        <v>0.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.4</v>
+        <v>0.393</v>
       </c>
       <c r="AK12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AL12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.322</v>
+        <v>0.344</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>735:20</t>
+          <t>784:18</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>307.6</v>
+        <v>334.76</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.569</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.608</v>
+        <v>0.615</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.014</v>
+        <v>1.025</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.166</v>
+        <v>0.167</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.309</v>
+        <v>0.335</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.706</v>
+        <v>1.679</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.192</v>
+        <v>0.195</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.156</v>
+        <v>0.159</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.107</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="13">
@@ -2354,7 +2354,7 @@
         <v>1.533</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.197</v>
+        <v>0.196</v>
       </c>
       <c r="AW13" t="n">
         <v>0.012</v>
@@ -2363,7 +2363,7 @@
         <v>0.061</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="14">
@@ -2373,22 +2373,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H14" t="n">
         <v>12</v>
@@ -2397,10 +2397,10 @@
         <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L14" t="n">
         <v>5</v>
@@ -2415,25 +2415,25 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="S14" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="T14" t="n">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="U14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="W14" t="n">
         <v>6</v>
@@ -2451,22 +2451,22 @@
         <v>0.667</v>
       </c>
       <c r="AB14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="AE14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.6</v>
+        <v>0.588</v>
       </c>
       <c r="AH14" t="n">
         <v>1</v>
@@ -2478,51 +2478,51 @@
         <v>0.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AL14" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.281</v>
+        <v>0.333</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>255:09</t>
+          <t>279:07</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>92.48</v>
+        <v>101.48</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.475</v>
+        <v>0.522</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.511</v>
+        <v>0.55</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.757</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.26</v>
+        <v>0.256</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.197</v>
+        <v>0.176</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.167</v>
+        <v>2.077</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.167</v>
+        <v>0.166</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.141</v>
+        <v>0.137</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.058</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="15">
@@ -2532,34 +2532,34 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C15" t="n">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="D15" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E15" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F15" t="n">
         <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H15" t="n">
+        <v>61</v>
+      </c>
+      <c r="I15" t="n">
+        <v>82</v>
+      </c>
+      <c r="J15" t="n">
+        <v>18</v>
+      </c>
+      <c r="K15" t="n">
         <v>56</v>
-      </c>
-      <c r="I15" t="n">
-        <v>77</v>
-      </c>
-      <c r="J15" t="n">
-        <v>17</v>
-      </c>
-      <c r="K15" t="n">
-        <v>55</v>
       </c>
       <c r="L15" t="n">
         <v>28</v>
@@ -2580,34 +2580,34 @@
         <v>22</v>
       </c>
       <c r="R15" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="S15" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="T15" t="n">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="U15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="V15" t="n">
         <v>27</v>
       </c>
       <c r="W15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="X15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y15" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="Z15" t="n">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.786</v>
+        <v>0.793</v>
       </c>
       <c r="AB15" t="n">
         <v>10</v>
@@ -2619,13 +2619,13 @@
         <v>0.476</v>
       </c>
       <c r="AE15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
@@ -2640,45 +2640,45 @@
         <v>4</v>
       </c>
       <c r="AL15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.333</v>
+        <v>0.308</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>349:33</t>
+          <t>369:24</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>151.88</v>
+        <v>160.08</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.724</v>
+        <v>0.728</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.238</v>
+        <v>1.256</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.145</v>
+        <v>0.137</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.583</v>
+        <v>0.598</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.773</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.2</v>
+        <v>0.198</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.09</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.177</v>
+        <v>0.17</v>
       </c>
       <c r="AY15" t="n">
         <v>0.02</v>
@@ -2691,16 +2691,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C16" t="n">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="D16" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E16" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2709,49 +2709,49 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I16" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="J16" t="n">
         <v>9</v>
       </c>
       <c r="K16" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L16" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="M16" t="n">
         <v>8</v>
       </c>
       <c r="N16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="Q16" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="R16" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="S16" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="T16" t="n">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="U16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V16" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="W16" t="n">
         <v>6</v>
@@ -2760,22 +2760,22 @@
         <v>3</v>
       </c>
       <c r="Y16" t="n">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="Z16" t="n">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="AB16" t="n">
         <v>8</v>
       </c>
       <c r="AC16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.381</v>
+        <v>0.348</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -2806,41 +2806,41 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>396:44</t>
+          <t>422:42</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>148.32</v>
+        <v>171.72</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.765</v>
+        <v>0.748</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.762</v>
+        <v>0.746</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.247</v>
+        <v>1.205</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.182</v>
+        <v>0.192</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.357</v>
+        <v>0.369</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.333</v>
+        <v>0.273</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.172</v>
+        <v>0.186</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.147</v>
+        <v>0.149</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="17">
@@ -2850,67 +2850,67 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I17" t="n">
+        <v>12</v>
+      </c>
+      <c r="J17" t="n">
+        <v>18</v>
+      </c>
+      <c r="K17" t="n">
+        <v>12</v>
+      </c>
+      <c r="L17" t="n">
         <v>8</v>
-      </c>
-      <c r="J17" t="n">
-        <v>11</v>
-      </c>
-      <c r="K17" t="n">
-        <v>6</v>
-      </c>
-      <c r="L17" t="n">
-        <v>5</v>
       </c>
       <c r="M17" t="n">
         <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="U17" t="n">
         <v>4</v>
       </c>
       <c r="V17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W17" t="n">
         <v>3</v>
@@ -2919,19 +2919,19 @@
         <v>3</v>
       </c>
       <c r="Y17" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Z17" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.611</v>
+        <v>0.531</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
@@ -2958,48 +2958,48 @@
         <v>2</v>
       </c>
       <c r="AL17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>71:35</t>
+          <t>109:31</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>29.52</v>
+        <v>49.28</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.476</v>
+        <v>0.417</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.489</v>
+        <v>0.424</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.169</v>
+        <v>0.162</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.19</v>
+        <v>0.139</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.19</v>
+        <v>0.206</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.078</v>
+        <v>0.081</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.094</v>
+        <v>0.123</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.012</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="18">
@@ -3009,22 +3009,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="D18" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E18" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F18" t="n">
         <v>20</v>
       </c>
       <c r="G18" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H18" t="n">
         <v>12</v>
@@ -3033,16 +3033,16 @@
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K18" t="n">
         <v>39</v>
       </c>
       <c r="L18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M18" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N18" t="n">
         <v>10</v>
@@ -3051,40 +3051,40 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R18" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="S18" t="n">
         <v>18</v>
       </c>
       <c r="T18" t="n">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="U18" t="n">
         <v>31</v>
       </c>
       <c r="V18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="W18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y18" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="Z18" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.681</v>
+        <v>0.707</v>
       </c>
       <c r="AB18" t="n">
         <v>4</v>
@@ -3108,10 +3108,10 @@
         <v>7</v>
       </c>
       <c r="AI18" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.292</v>
+        <v>0.269</v>
       </c>
       <c r="AK18" t="n">
         <v>13</v>
@@ -3124,41 +3124,41 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>448:22</t>
+          <t>484:16</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>139.56</v>
+        <v>148.56</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.612</v>
+        <v>0.621</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.608</v>
+        <v>0.617</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.103</v>
+        <v>1.117</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.103</v>
+        <v>0.097</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.308</v>
+        <v>1.357</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.143</v>
+        <v>0.14</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.045</v>
+        <v>0.046</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.098</v>
+        <v>0.09</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="19">
@@ -3168,37 +3168,37 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>32</v>
+      </c>
+      <c r="C19" t="n">
+        <v>144</v>
+      </c>
+      <c r="D19" t="n">
+        <v>33</v>
+      </c>
+      <c r="E19" t="n">
+        <v>57</v>
+      </c>
+      <c r="F19" t="n">
+        <v>21</v>
+      </c>
+      <c r="G19" t="n">
+        <v>70</v>
+      </c>
+      <c r="H19" t="n">
+        <v>15</v>
+      </c>
+      <c r="I19" t="n">
+        <v>24</v>
+      </c>
+      <c r="J19" t="n">
         <v>30</v>
       </c>
-      <c r="C19" t="n">
-        <v>132</v>
-      </c>
-      <c r="D19" t="n">
-        <v>31</v>
-      </c>
-      <c r="E19" t="n">
-        <v>53</v>
-      </c>
-      <c r="F19" t="n">
-        <v>19</v>
-      </c>
-      <c r="G19" t="n">
-        <v>64</v>
-      </c>
-      <c r="H19" t="n">
-        <v>13</v>
-      </c>
-      <c r="I19" t="n">
-        <v>21</v>
-      </c>
-      <c r="J19" t="n">
-        <v>28</v>
-      </c>
       <c r="K19" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M19" t="n">
         <v>12</v>
@@ -3210,25 +3210,25 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q19" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R19" t="n">
+        <v>35</v>
+      </c>
+      <c r="S19" t="n">
         <v>30</v>
       </c>
-      <c r="S19" t="n">
-        <v>28</v>
-      </c>
       <c r="T19" t="n">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="U19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W19" t="n">
         <v>24</v>
@@ -3237,84 +3237,84 @@
         <v>12</v>
       </c>
       <c r="Y19" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="Z19" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.738</v>
+        <v>0.745</v>
       </c>
       <c r="AB19" t="n">
         <v>7</v>
       </c>
       <c r="AC19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.412</v>
+        <v>0.389</v>
       </c>
       <c r="AE19" t="n">
         <v>6</v>
       </c>
       <c r="AF19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="AH19" t="n">
         <v>9</v>
       </c>
       <c r="AI19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.391</v>
+        <v>0.375</v>
       </c>
       <c r="AK19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL19" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.244</v>
+        <v>0.261</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>359:43</t>
+          <t>386:35</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>158.24</v>
+        <v>170.56</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.509</v>
+        <v>0.508</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.523</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.834</v>
+        <v>0.844</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.202</v>
+        <v>0.193</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.111</v>
+        <v>0.118</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.875</v>
+        <v>0.909</v>
       </c>
       <c r="AV19" t="n">
         <v>0.202</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.05</v>
+        <v>0.052</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.162</v>
+        <v>0.163</v>
       </c>
       <c r="AY19" t="n">
         <v>0.032</v>
@@ -3327,67 +3327,67 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C20" t="n">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E20" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F20" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G20" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H20" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I20" t="n">
+        <v>25</v>
+      </c>
+      <c r="J20" t="n">
+        <v>19</v>
+      </c>
+      <c r="K20" t="n">
+        <v>66</v>
+      </c>
+      <c r="L20" t="n">
+        <v>18</v>
+      </c>
+      <c r="M20" t="n">
+        <v>10</v>
+      </c>
+      <c r="N20" t="n">
+        <v>18</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>9</v>
+      </c>
+      <c r="R20" t="n">
+        <v>36</v>
+      </c>
+      <c r="S20" t="n">
+        <v>23</v>
+      </c>
+      <c r="T20" t="n">
+        <v>198</v>
+      </c>
+      <c r="U20" t="n">
         <v>21</v>
       </c>
-      <c r="J20" t="n">
-        <v>16</v>
-      </c>
-      <c r="K20" t="n">
-        <v>63</v>
-      </c>
-      <c r="L20" t="n">
-        <v>16</v>
-      </c>
-      <c r="M20" t="n">
-        <v>8</v>
-      </c>
-      <c r="N20" t="n">
-        <v>16</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>8</v>
-      </c>
-      <c r="R20" t="n">
-        <v>32</v>
-      </c>
-      <c r="S20" t="n">
-        <v>18</v>
-      </c>
-      <c r="T20" t="n">
-        <v>175</v>
-      </c>
-      <c r="U20" t="n">
-        <v>18</v>
-      </c>
       <c r="V20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W20" t="n">
         <v>11</v>
@@ -3396,87 +3396,87 @@
         <v>4</v>
       </c>
       <c r="Y20" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="Z20" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="AB20" t="n">
         <v>1</v>
       </c>
       <c r="AC20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="AE20" t="n">
         <v>7</v>
       </c>
       <c r="AF20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.35</v>
+        <v>0.333</v>
       </c>
       <c r="AH20" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AI20" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.455</v>
+        <v>0.472</v>
       </c>
       <c r="AK20" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL20" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.339</v>
+        <v>0.344</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>491:07</t>
+          <t>531:12</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>146.24</v>
+        <v>163</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.55</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.571</v>
+        <v>0.578</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.08</v>
+        <v>1.092</v>
       </c>
       <c r="AS20" t="n">
         <v>0.055</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.124</v>
+        <v>0.126</v>
       </c>
       <c r="AU20" t="n">
-        <v>2</v>
+        <v>2.111</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.137</v>
+        <v>0.14</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.036</v>
+        <v>0.038</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.144</v>
+        <v>0.14</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.018</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="21">
@@ -3486,16 +3486,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C21" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="D21" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E21" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -3504,70 +3504,70 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I21" t="n">
+        <v>49</v>
+      </c>
+      <c r="J21" t="n">
+        <v>52</v>
+      </c>
+      <c r="K21" t="n">
+        <v>57</v>
+      </c>
+      <c r="L21" t="n">
+        <v>36</v>
+      </c>
+      <c r="M21" t="n">
+        <v>14</v>
+      </c>
+      <c r="N21" t="n">
+        <v>20</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>27</v>
+      </c>
+      <c r="R21" t="n">
         <v>45</v>
       </c>
-      <c r="J21" t="n">
-        <v>51</v>
-      </c>
-      <c r="K21" t="n">
-        <v>55</v>
-      </c>
-      <c r="L21" t="n">
-        <v>34</v>
-      </c>
-      <c r="M21" t="n">
-        <v>13</v>
-      </c>
-      <c r="N21" t="n">
-        <v>19</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>24</v>
-      </c>
-      <c r="R21" t="n">
-        <v>41</v>
-      </c>
       <c r="S21" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="T21" t="n">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="U21" t="n">
         <v>6</v>
       </c>
       <c r="V21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Z21" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.724</v>
+        <v>0.714</v>
       </c>
       <c r="AB21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC21" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="AD21" t="n">
         <v>0.333</v>
@@ -3576,10 +3576,10 @@
         <v>8</v>
       </c>
       <c r="AF21" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.333</v>
+        <v>0.308</v>
       </c>
       <c r="AH21" t="n">
         <v>0</v>
@@ -3601,41 +3601,41 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>461:51</t>
+          <t>493:02</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>162.8</v>
+        <v>175.56</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.513</v>
+        <v>0.504</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.555</v>
+        <v>0.545</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.946</v>
+        <v>0.923</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.147</v>
+        <v>0.154</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.269</v>
+        <v>0.268</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.125</v>
+        <v>1.926</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.162</v>
+        <v>0.163</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.082</v>
+        <v>0.081</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.134</v>
+        <v>0.13</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.059</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="22">
@@ -3785,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.406</v>
+        <v>0.404</v>
       </c>
       <c r="AW22" t="n">
         <v>0</v>
@@ -4103,7 +4103,7 @@
         <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.197</v>
+        <v>0.196</v>
       </c>
       <c r="AW24" t="n">
         <v>0</v>
@@ -4122,7 +4122,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -4149,10 +4149,10 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L25" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -4164,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4281,153 +4281,153 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C26" t="n">
-        <v>2673</v>
+        <v>2856</v>
       </c>
       <c r="D26" t="n">
-        <v>678</v>
+        <v>723</v>
       </c>
       <c r="E26" t="n">
-        <v>1243</v>
+        <v>1329</v>
       </c>
       <c r="F26" t="n">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="G26" t="n">
-        <v>771</v>
+        <v>817</v>
       </c>
       <c r="H26" t="n">
-        <v>579</v>
+        <v>618</v>
       </c>
       <c r="I26" t="n">
-        <v>762</v>
+        <v>818</v>
       </c>
       <c r="J26" t="n">
-        <v>546</v>
+        <v>583</v>
       </c>
       <c r="K26" t="n">
-        <v>812</v>
+        <v>852</v>
       </c>
       <c r="L26" t="n">
-        <v>334</v>
+        <v>359</v>
       </c>
       <c r="M26" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="N26" t="n">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>434</v>
+        <v>466</v>
       </c>
       <c r="Q26" t="n">
-        <v>407</v>
+        <v>438</v>
       </c>
       <c r="R26" t="n">
-        <v>777</v>
+        <v>828</v>
       </c>
       <c r="S26" t="n">
-        <v>707</v>
+        <v>756</v>
       </c>
       <c r="T26" t="n">
-        <v>3002</v>
+        <v>3191</v>
       </c>
       <c r="U26" t="n">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="V26" t="n">
-        <v>327</v>
+        <v>361</v>
       </c>
       <c r="W26" t="n">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="X26" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="Y26" t="n">
-        <v>1038</v>
+        <v>1113</v>
       </c>
       <c r="Z26" t="n">
-        <v>1386</v>
+        <v>1496</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.749</v>
+        <v>0.744</v>
       </c>
       <c r="AB26" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AC26" t="n">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.378</v>
+        <v>0.377</v>
       </c>
       <c r="AE26" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AF26" t="n">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.328</v>
+        <v>0.322</v>
       </c>
       <c r="AH26" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AI26" t="n">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.376</v>
+        <v>0.379</v>
       </c>
       <c r="AK26" t="n">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="AL26" t="n">
-        <v>585</v>
+        <v>619</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.301</v>
+        <v>0.305</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>6400:00</t>
+          <t>6800:00</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>2783.28</v>
+        <v>2971.92</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.52</v>
+        <v>0.521</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.569</v>
+        <v>0.57</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.96</v>
+        <v>0.961</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.156</v>
+        <v>0.157</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.287</v>
+        <v>0.288</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.258</v>
+        <v>1.251</v>
       </c>
       <c r="AV26" t="n">
         <v>0.2</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.058</v>
+        <v>0.059</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.142</v>
+        <v>0.141</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
@@ -4440,153 +4440,153 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C27" t="n">
-        <v>2865</v>
+        <v>3097</v>
       </c>
       <c r="D27" t="n">
-        <v>601</v>
+        <v>652</v>
       </c>
       <c r="E27" t="n">
-        <v>1103</v>
+        <v>1184</v>
       </c>
       <c r="F27" t="n">
-        <v>342</v>
+        <v>372</v>
       </c>
       <c r="G27" t="n">
-        <v>953</v>
+        <v>1021</v>
       </c>
       <c r="H27" t="n">
-        <v>637</v>
+        <v>677</v>
       </c>
       <c r="I27" t="n">
-        <v>819</v>
+        <v>868</v>
       </c>
       <c r="J27" t="n">
-        <v>552</v>
+        <v>586</v>
       </c>
       <c r="K27" t="n">
-        <v>810</v>
+        <v>861</v>
       </c>
       <c r="L27" t="n">
-        <v>329</v>
+        <v>359</v>
       </c>
       <c r="M27" t="n">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="N27" t="n">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="Q27" t="n">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="R27" t="n">
-        <v>715</v>
+        <v>764</v>
       </c>
       <c r="S27" t="n">
-        <v>760</v>
+        <v>811</v>
       </c>
       <c r="T27" t="n">
-        <v>3351</v>
+        <v>3630</v>
       </c>
       <c r="U27" t="n">
-        <v>348</v>
+        <v>378</v>
       </c>
       <c r="V27" t="n">
-        <v>337</v>
+        <v>381</v>
       </c>
       <c r="W27" t="n">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="X27" t="n">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="Y27" t="n">
-        <v>1013</v>
+        <v>1089</v>
       </c>
       <c r="Z27" t="n">
-        <v>1296</v>
+        <v>1392</v>
       </c>
       <c r="AA27" t="n">
         <v>0.782</v>
       </c>
       <c r="AB27" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AC27" t="n">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.367</v>
+        <v>0.365</v>
       </c>
       <c r="AE27" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="AF27" t="n">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.352</v>
+        <v>0.363</v>
       </c>
       <c r="AH27" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="AI27" t="n">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="AJ27" t="n">
         <v>0.406</v>
       </c>
       <c r="AK27" t="n">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="AL27" t="n">
-        <v>709</v>
+        <v>760</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.343</v>
+        <v>0.35</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>6400:00</t>
+          <t>6800:00</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>2802.36</v>
+        <v>2995.92</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.542</v>
+        <v>0.549</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.593</v>
+        <v>0.599</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.022</v>
+        <v>1.034</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.138</v>
+        <v>0.137</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.31</v>
+        <v>0.307</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.43</v>
+        <v>1.433</v>
       </c>
       <c r="AV27" t="n">
         <v>0.2</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.058</v>
+        <v>0.059</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.142</v>
+        <v>0.141</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -4656,156 +4656,156 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C29" t="n">
-        <v>15.387</v>
+        <v>14.879</v>
       </c>
       <c r="D29" t="n">
-        <v>2.548</v>
+        <v>2.455</v>
       </c>
       <c r="E29" t="n">
-        <v>5.226</v>
+        <v>5.121</v>
       </c>
       <c r="F29" t="n">
-        <v>1.645</v>
+        <v>1.636</v>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>4.97</v>
       </c>
       <c r="H29" t="n">
-        <v>5.355</v>
+        <v>5.061</v>
       </c>
       <c r="I29" t="n">
-        <v>6.065</v>
+        <v>5.758</v>
       </c>
       <c r="J29" t="n">
-        <v>2.806</v>
+        <v>2.758</v>
       </c>
       <c r="K29" t="n">
-        <v>1.419</v>
+        <v>1.333</v>
       </c>
       <c r="L29" t="n">
-        <v>0.839</v>
+        <v>0.788</v>
       </c>
       <c r="M29" t="n">
-        <v>0.871</v>
+        <v>0.848</v>
       </c>
       <c r="N29" t="n">
-        <v>0.742</v>
+        <v>0.697</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.613</v>
+        <v>1.697</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.613</v>
+        <v>1.697</v>
       </c>
       <c r="R29" t="n">
-        <v>2.581</v>
+        <v>2.576</v>
       </c>
       <c r="S29" t="n">
-        <v>5.097</v>
+        <v>4.848</v>
       </c>
       <c r="T29" t="n">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="U29" t="n">
-        <v>2.387</v>
+        <v>2.242</v>
       </c>
       <c r="V29" t="n">
-        <v>1.323</v>
+        <v>1.242</v>
       </c>
       <c r="W29" t="n">
-        <v>1.161</v>
+        <v>1.091</v>
       </c>
       <c r="X29" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.879</v>
       </c>
       <c r="Y29" t="n">
-        <v>6.742</v>
+        <v>6.394</v>
       </c>
       <c r="Z29" t="n">
-        <v>8.355</v>
+        <v>8</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.799</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.742</v>
+        <v>0.727</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.677</v>
+        <v>1.636</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.442</v>
+        <v>0.444</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.419</v>
+        <v>0.394</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.258</v>
+        <v>1.242</v>
       </c>
       <c r="AG29" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="AH29" t="n">
         <v>0.333</v>
       </c>
-      <c r="AH29" t="n">
-        <v>0.323</v>
-      </c>
       <c r="AI29" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.323</v>
+        <v>0.344</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.323</v>
+        <v>1.303</v>
       </c>
       <c r="AL29" t="n">
         <v>4</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.331</v>
+        <v>0.326</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>25:41</t>
+          <t>25:13</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>14.507</v>
+        <v>14.321</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.491</v>
+        <v>0.486</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.597</v>
+        <v>0.589</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.061</v>
+        <v>1.039</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.111</v>
+        <v>0.118</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.524</v>
+        <v>0.502</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.74</v>
+        <v>1.625</v>
       </c>
       <c r="AV29" t="n">
         <v>0.26</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.037</v>
+        <v>0.035</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.114</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="30">
@@ -4815,156 +4815,156 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C30" t="n">
-        <v>3.875</v>
+        <v>3.758</v>
       </c>
       <c r="D30" t="n">
-        <v>0.781</v>
+        <v>0.758</v>
       </c>
       <c r="E30" t="n">
-        <v>1.625</v>
+        <v>1.606</v>
       </c>
       <c r="F30" t="n">
-        <v>0.469</v>
+        <v>0.455</v>
       </c>
       <c r="G30" t="n">
-        <v>2.156</v>
+        <v>2.121</v>
       </c>
       <c r="H30" t="n">
-        <v>0.906</v>
+        <v>0.879</v>
       </c>
       <c r="I30" t="n">
-        <v>1.125</v>
+        <v>1.091</v>
       </c>
       <c r="J30" t="n">
-        <v>1.531</v>
+        <v>1.515</v>
       </c>
       <c r="K30" t="n">
-        <v>1.562</v>
+        <v>1.606</v>
       </c>
       <c r="L30" t="n">
-        <v>0.281</v>
+        <v>0.273</v>
       </c>
       <c r="M30" t="n">
-        <v>0.656</v>
+        <v>0.636</v>
       </c>
       <c r="N30" t="n">
-        <v>0.25</v>
+        <v>0.273</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.125</v>
+        <v>1.121</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.125</v>
+        <v>1.121</v>
       </c>
       <c r="R30" t="n">
-        <v>2.062</v>
+        <v>2.03</v>
       </c>
       <c r="S30" t="n">
-        <v>1.312</v>
+        <v>1.303</v>
       </c>
       <c r="T30" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="U30" t="n">
-        <v>0.656</v>
+        <v>0.636</v>
       </c>
       <c r="V30" t="n">
-        <v>0.375</v>
+        <v>0.364</v>
       </c>
       <c r="W30" t="n">
-        <v>0.188</v>
+        <v>0.182</v>
       </c>
       <c r="X30" t="n">
-        <v>0.125</v>
+        <v>0.121</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.438</v>
+        <v>1.394</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.875</v>
+        <v>1.818</v>
       </c>
       <c r="AA30" t="n">
         <v>0.767</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.156</v>
+        <v>0.152</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.438</v>
+        <v>0.424</v>
       </c>
       <c r="AD30" t="n">
         <v>0.357</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.094</v>
+        <v>0.091</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.438</v>
+        <v>0.455</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.214</v>
+        <v>0.2</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.281</v>
+        <v>0.273</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.531</v>
+        <v>0.515</v>
       </c>
       <c r="AJ30" t="n">
         <v>0.529</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.188</v>
+        <v>0.182</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.625</v>
+        <v>1.606</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.115</v>
+        <v>0.113</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>5.401</v>
+        <v>5.328</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.393</v>
+        <v>0.386</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.453</v>
+        <v>0.447</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.717</v>
+        <v>0.705</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.208</v>
+        <v>0.21</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.24</v>
+        <v>0.236</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.361</v>
+        <v>1.351</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.147</v>
+        <v>0.146</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.104</v>
+        <v>0.108</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.055</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="31">
@@ -4974,156 +4974,156 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C31" t="n">
-        <v>12.194</v>
+        <v>11.939</v>
       </c>
       <c r="D31" t="n">
-        <v>3.323</v>
+        <v>3.212</v>
       </c>
       <c r="E31" t="n">
-        <v>6.29</v>
+        <v>6.091</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="G31" t="n">
-        <v>2.71</v>
+        <v>2.606</v>
       </c>
       <c r="H31" t="n">
-        <v>2.548</v>
+        <v>2.606</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>3.061</v>
       </c>
       <c r="J31" t="n">
-        <v>1.032</v>
+        <v>1.061</v>
       </c>
       <c r="K31" t="n">
-        <v>4.129</v>
+        <v>3.97</v>
       </c>
       <c r="L31" t="n">
-        <v>1.355</v>
+        <v>1.333</v>
       </c>
       <c r="M31" t="n">
-        <v>0.774</v>
+        <v>0.727</v>
       </c>
       <c r="N31" t="n">
-        <v>1.161</v>
+        <v>1.091</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.548</v>
+        <v>1.485</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.548</v>
+        <v>1.485</v>
       </c>
       <c r="R31" t="n">
-        <v>2.839</v>
+        <v>2.818</v>
       </c>
       <c r="S31" t="n">
-        <v>2.871</v>
+        <v>2.97</v>
       </c>
       <c r="T31" t="n">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="U31" t="n">
-        <v>1.548</v>
+        <v>1.576</v>
       </c>
       <c r="V31" t="n">
-        <v>1.548</v>
+        <v>1.697</v>
       </c>
       <c r="W31" t="n">
-        <v>0.903</v>
+        <v>0.848</v>
       </c>
       <c r="X31" t="n">
-        <v>0.548</v>
+        <v>0.515</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.645</v>
+        <v>4.636</v>
       </c>
       <c r="Z31" t="n">
-        <v>6.032</v>
+        <v>6.03</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.774</v>
+        <v>0.758</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.742</v>
+        <v>1.667</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.444</v>
+        <v>0.455</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.452</v>
+        <v>0.424</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.516</v>
+        <v>1.455</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.298</v>
+        <v>0.292</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.161</v>
+        <v>0.152</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.581</v>
+        <v>0.545</v>
       </c>
       <c r="AJ31" t="n">
         <v>0.278</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.839</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.129</v>
+        <v>2.061</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.394</v>
+        <v>0.397</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>25:18</t>
+          <t>24:50</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>11.868</v>
+        <v>11.528</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.536</v>
+        <v>0.537</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.591</v>
+        <v>0.594</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.027</v>
+        <v>1.036</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.13</v>
+        <v>0.129</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.283</v>
+        <v>0.3</v>
       </c>
       <c r="AU31" t="n">
-        <v>0.667</v>
+        <v>0.714</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.216</v>
+        <v>0.212</v>
       </c>
       <c r="AW31" t="n">
         <v>0.06</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.183</v>
+        <v>0.179</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.042</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="32">
@@ -5133,153 +5133,153 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C32" t="n">
-        <v>7.938</v>
+        <v>7.794</v>
       </c>
       <c r="D32" t="n">
-        <v>2.25</v>
+        <v>2.206</v>
       </c>
       <c r="E32" t="n">
-        <v>5.656</v>
+        <v>5.5</v>
       </c>
       <c r="F32" t="n">
-        <v>0.719</v>
+        <v>0.706</v>
       </c>
       <c r="G32" t="n">
-        <v>2.656</v>
+        <v>2.588</v>
       </c>
       <c r="H32" t="n">
-        <v>1.281</v>
+        <v>1.265</v>
       </c>
       <c r="I32" t="n">
-        <v>1.969</v>
+        <v>1.912</v>
       </c>
       <c r="J32" t="n">
-        <v>2.031</v>
+        <v>2.029</v>
       </c>
       <c r="K32" t="n">
-        <v>1.969</v>
+        <v>1.882</v>
       </c>
       <c r="L32" t="n">
-        <v>0.844</v>
+        <v>0.853</v>
       </c>
       <c r="M32" t="n">
-        <v>1.031</v>
+        <v>1.029</v>
       </c>
       <c r="N32" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.529</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.562</v>
+        <v>1.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.562</v>
+        <v>1.5</v>
       </c>
       <c r="R32" t="n">
-        <v>3.094</v>
+        <v>3.088</v>
       </c>
       <c r="S32" t="n">
-        <v>2.062</v>
+        <v>1.971</v>
       </c>
       <c r="T32" t="n">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="U32" t="n">
-        <v>1.156</v>
+        <v>1.088</v>
       </c>
       <c r="V32" t="n">
-        <v>1.031</v>
+        <v>0.971</v>
       </c>
       <c r="W32" t="n">
-        <v>0.125</v>
+        <v>0.118</v>
       </c>
       <c r="X32" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.5</v>
+        <v>2.412</v>
       </c>
       <c r="Z32" t="n">
-        <v>4.125</v>
+        <v>3.971</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.606</v>
+        <v>0.607</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.438</v>
+        <v>0.441</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.625</v>
+        <v>1.559</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.269</v>
+        <v>0.283</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.594</v>
+        <v>0.618</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.875</v>
+        <v>1.882</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.317</v>
+        <v>0.328</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.062</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.188</v>
+        <v>0.206</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.656</v>
+        <v>0.618</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.469</v>
+        <v>2.382</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.266</v>
+        <v>0.259</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>10.741</v>
+        <v>10.429</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.4</v>
+        <v>0.404</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.432</v>
+        <v>0.436</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.739</v>
+        <v>0.747</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.145</v>
+        <v>0.144</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.154</v>
+        <v>0.156</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.3</v>
+        <v>1.353</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.297</v>
+        <v>0.29</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.057</v>
+        <v>0.058</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.133</v>
+        <v>0.128</v>
       </c>
       <c r="AY32" t="n">
         <v>0.078</v>
@@ -5292,156 +5292,156 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C33" t="n">
-        <v>9.75</v>
+        <v>10.088</v>
       </c>
       <c r="D33" t="n">
-        <v>2.469</v>
+        <v>2.441</v>
       </c>
       <c r="E33" t="n">
-        <v>4.156</v>
+        <v>4.147</v>
       </c>
       <c r="F33" t="n">
-        <v>0.906</v>
+        <v>0.971</v>
       </c>
       <c r="G33" t="n">
-        <v>2.625</v>
+        <v>2.706</v>
       </c>
       <c r="H33" t="n">
-        <v>2.094</v>
+        <v>2.294</v>
       </c>
       <c r="I33" t="n">
-        <v>2.812</v>
+        <v>3.059</v>
       </c>
       <c r="J33" t="n">
-        <v>2.719</v>
+        <v>2.765</v>
       </c>
       <c r="K33" t="n">
-        <v>3.188</v>
+        <v>3.265</v>
       </c>
       <c r="L33" t="n">
-        <v>0.625</v>
+        <v>0.588</v>
       </c>
       <c r="M33" t="n">
-        <v>0.625</v>
+        <v>0.735</v>
       </c>
       <c r="N33" t="n">
-        <v>0.25</v>
+        <v>0.265</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.594</v>
+        <v>1.647</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.594</v>
+        <v>1.647</v>
       </c>
       <c r="R33" t="n">
-        <v>1.438</v>
+        <v>1.441</v>
       </c>
       <c r="S33" t="n">
-        <v>2.75</v>
+        <v>2.941</v>
       </c>
       <c r="T33" t="n">
-        <v>408</v>
+        <v>454</v>
       </c>
       <c r="U33" t="n">
-        <v>1.219</v>
+        <v>1.382</v>
       </c>
       <c r="V33" t="n">
-        <v>0.781</v>
+        <v>0.824</v>
       </c>
       <c r="W33" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.882</v>
       </c>
       <c r="X33" t="n">
-        <v>0.406</v>
+        <v>0.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>4.031</v>
+        <v>4.235</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.406</v>
+        <v>5.676</v>
       </c>
       <c r="AA33" t="n">
         <v>0.746</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.312</v>
+        <v>0.294</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.719</v>
+        <v>0.706</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.435</v>
+        <v>0.417</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.219</v>
+        <v>0.206</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.844</v>
+        <v>0.824</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.259</v>
+        <v>0.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.312</v>
+        <v>0.324</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.781</v>
+        <v>0.824</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.4</v>
+        <v>0.393</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.594</v>
+        <v>0.647</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.844</v>
+        <v>1.882</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.322</v>
+        <v>0.344</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>9.612</v>
+        <v>9.846</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.569</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.608</v>
+        <v>0.615</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.014</v>
+        <v>1.025</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.166</v>
+        <v>0.167</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.309</v>
+        <v>0.335</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.706</v>
+        <v>1.679</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.192</v>
+        <v>0.195</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.156</v>
+        <v>0.159</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.107</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="34">
@@ -5451,41 +5451,41 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C34" t="n">
-        <v>5.833</v>
+        <v>5.929</v>
       </c>
       <c r="D34" t="n">
-        <v>1.167</v>
+        <v>1.143</v>
       </c>
       <c r="E34" t="n">
-        <v>2.25</v>
+        <v>2.143</v>
       </c>
       <c r="F34" t="n">
-        <v>0.833</v>
+        <v>0.929</v>
       </c>
       <c r="G34" t="n">
-        <v>2.833</v>
+        <v>2.714</v>
       </c>
       <c r="H34" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.214</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.857</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.429</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="M34" t="n">
         <v>1</v>
       </c>
-      <c r="I34" t="n">
-        <v>1.417</v>
-      </c>
-      <c r="J34" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="K34" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1.167</v>
-      </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
@@ -5493,114 +5493,114 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>1.857</v>
       </c>
       <c r="Q34" t="n">
-        <v>2</v>
+        <v>1.857</v>
       </c>
       <c r="R34" t="n">
-        <v>3.667</v>
+        <v>3.286</v>
       </c>
       <c r="S34" t="n">
-        <v>2.167</v>
+        <v>2.143</v>
       </c>
       <c r="T34" t="n">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="U34" t="n">
-        <v>0.583</v>
+        <v>0.714</v>
       </c>
       <c r="V34" t="n">
-        <v>0.667</v>
+        <v>0.786</v>
       </c>
       <c r="W34" t="n">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="X34" t="n">
-        <v>0.417</v>
+        <v>0.357</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.333</v>
+        <v>1.143</v>
       </c>
       <c r="Z34" t="n">
-        <v>2</v>
+        <v>1.714</v>
       </c>
       <c r="AA34" t="n">
         <v>0.667</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.083</v>
+        <v>0.143</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.417</v>
+        <v>0.429</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.75</v>
+        <v>0.714</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.25</v>
+        <v>1.214</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.6</v>
+        <v>0.588</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.083</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="AJ34" t="n">
         <v>0.5</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.75</v>
+        <v>0.857</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.667</v>
+        <v>2.571</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.281</v>
+        <v>0.333</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>7.707</v>
+        <v>7.249</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.475</v>
+        <v>0.522</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.511</v>
+        <v>0.55</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.757</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.26</v>
+        <v>0.256</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.197</v>
+        <v>0.176</v>
       </c>
       <c r="AU34" t="n">
-        <v>2.167</v>
+        <v>2.077</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.167</v>
+        <v>0.166</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.141</v>
+        <v>0.137</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.161</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="35">
@@ -5750,7 +5750,7 @@
         <v>1.533</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.197</v>
+        <v>0.196</v>
       </c>
       <c r="AW35" t="n">
         <v>0.012</v>
@@ -5769,100 +5769,100 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C36" t="n">
-        <v>7.833</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="E36" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="F36" t="n">
-        <v>0.167</v>
+        <v>0.16</v>
       </c>
       <c r="G36" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="H36" t="n">
-        <v>2.333</v>
+        <v>2.44</v>
       </c>
       <c r="I36" t="n">
-        <v>3.208</v>
+        <v>3.28</v>
       </c>
       <c r="J36" t="n">
-        <v>0.708</v>
+        <v>0.72</v>
       </c>
       <c r="K36" t="n">
-        <v>2.292</v>
+        <v>2.24</v>
       </c>
       <c r="L36" t="n">
-        <v>1.167</v>
+        <v>1.12</v>
       </c>
       <c r="M36" t="n">
-        <v>0.417</v>
+        <v>0.4</v>
       </c>
       <c r="N36" t="n">
-        <v>0.542</v>
+        <v>0.52</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.917</v>
+        <v>0.88</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.917</v>
+        <v>0.88</v>
       </c>
       <c r="R36" t="n">
-        <v>2.208</v>
+        <v>2.28</v>
       </c>
       <c r="S36" t="n">
-        <v>2.417</v>
+        <v>2.44</v>
       </c>
       <c r="T36" t="n">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="U36" t="n">
-        <v>0.833</v>
+        <v>0.88</v>
       </c>
       <c r="V36" t="n">
-        <v>1.125</v>
+        <v>1.08</v>
       </c>
       <c r="W36" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="X36" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="Y36" t="n">
-        <v>4.292</v>
+        <v>4.44</v>
       </c>
       <c r="Z36" t="n">
-        <v>5.458</v>
+        <v>5.6</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.786</v>
+        <v>0.793</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.417</v>
+        <v>0.4</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.875</v>
+        <v>0.84</v>
       </c>
       <c r="AD36" t="n">
         <v>0.476</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.125</v>
+        <v>0.16</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.375</v>
+        <v>0.4</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="AH36" t="n">
         <v>0</v>
@@ -5874,48 +5874,48 @@
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.167</v>
+        <v>0.16</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.333</v>
+        <v>0.308</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>6.328</v>
+        <v>6.403</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.724</v>
+        <v>0.728</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.238</v>
+        <v>1.256</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.145</v>
+        <v>0.137</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.583</v>
+        <v>0.598</v>
       </c>
       <c r="AU36" t="n">
-        <v>0.773</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.2</v>
+        <v>0.198</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.09</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.177</v>
+        <v>0.17</v>
       </c>
       <c r="AY36" t="n">
         <v>0.027</v>
@@ -5928,16 +5928,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C37" t="n">
-        <v>5.968</v>
+        <v>6.273</v>
       </c>
       <c r="D37" t="n">
-        <v>2.419</v>
+        <v>2.515</v>
       </c>
       <c r="E37" t="n">
-        <v>3.161</v>
+        <v>3.364</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -5946,79 +5946,79 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.129</v>
+        <v>1.242</v>
       </c>
       <c r="I37" t="n">
-        <v>1.71</v>
+        <v>1.909</v>
       </c>
       <c r="J37" t="n">
-        <v>0.29</v>
+        <v>0.273</v>
       </c>
       <c r="K37" t="n">
-        <v>1.677</v>
+        <v>1.697</v>
       </c>
       <c r="L37" t="n">
-        <v>1.484</v>
+        <v>1.606</v>
       </c>
       <c r="M37" t="n">
-        <v>0.258</v>
+        <v>0.242</v>
       </c>
       <c r="N37" t="n">
-        <v>1.032</v>
+        <v>1</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.871</v>
+        <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.871</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>2.774</v>
+        <v>2.788</v>
       </c>
       <c r="S37" t="n">
-        <v>1.323</v>
+        <v>1.424</v>
       </c>
       <c r="T37" t="n">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="U37" t="n">
-        <v>0.258</v>
+        <v>0.303</v>
       </c>
       <c r="V37" t="n">
-        <v>1.774</v>
+        <v>2</v>
       </c>
       <c r="W37" t="n">
-        <v>0.194</v>
+        <v>0.182</v>
       </c>
       <c r="X37" t="n">
-        <v>0.097</v>
+        <v>0.091</v>
       </c>
       <c r="Y37" t="n">
-        <v>3.194</v>
+        <v>3.424</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.935</v>
+        <v>4.333</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.258</v>
+        <v>0.242</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.677</v>
+        <v>0.697</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.381</v>
+        <v>0.348</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.097</v>
+        <v>0.091</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.258</v>
+        <v>0.242</v>
       </c>
       <c r="AG37" t="n">
         <v>0.375</v>
@@ -6043,41 +6043,41 @@
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>4.785</v>
+        <v>5.204</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.765</v>
+        <v>0.748</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.762</v>
+        <v>0.746</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.247</v>
+        <v>1.205</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.182</v>
+        <v>0.192</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.357</v>
+        <v>0.369</v>
       </c>
       <c r="AU37" t="n">
-        <v>0.333</v>
+        <v>0.273</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.172</v>
+        <v>0.186</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.147</v>
+        <v>0.149</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="38">
@@ -6087,52 +6087,52 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D38" t="n">
-        <v>0.875</v>
+        <v>1.2</v>
       </c>
       <c r="E38" t="n">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="F38" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="G38" t="n">
-        <v>0.875</v>
+        <v>0.9</v>
       </c>
       <c r="H38" t="n">
         <v>0.5</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
-        <v>1.375</v>
+        <v>1.8</v>
       </c>
       <c r="K38" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="L38" t="n">
-        <v>0.625</v>
+        <v>0.8</v>
       </c>
       <c r="M38" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="N38" t="n">
-        <v>0.375</v>
+        <v>0.7</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.625</v>
+        <v>0.8</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.625</v>
+        <v>0.8</v>
       </c>
       <c r="R38" t="n">
         <v>1.5</v>
@@ -6141,34 +6141,34 @@
         <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="U38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V38" t="n">
         <v>0.5</v>
       </c>
-      <c r="V38" t="n">
-        <v>0.375</v>
-      </c>
       <c r="W38" t="n">
-        <v>0.375</v>
+        <v>0.3</v>
       </c>
       <c r="X38" t="n">
-        <v>0.375</v>
+        <v>0.3</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.375</v>
+        <v>1.7</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.611</v>
+        <v>0.531</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.125</v>
+        <v>0.2</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -6186,57 +6186,57 @@
         <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.375</v>
+        <v>0.4</v>
       </c>
       <c r="AJ38" t="n">
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AL38" t="n">
         <v>0.5</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>3.69</v>
+        <v>4.928</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.476</v>
+        <v>0.417</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.489</v>
+        <v>0.424</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.169</v>
+        <v>0.162</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.19</v>
+        <v>0.139</v>
       </c>
       <c r="AU38" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.19</v>
+        <v>0.206</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.078</v>
+        <v>0.081</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.094</v>
+        <v>0.123</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.05</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="39">
@@ -6246,156 +6246,156 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C39" t="n">
-        <v>4.812</v>
+        <v>4.882</v>
       </c>
       <c r="D39" t="n">
-        <v>1.281</v>
+        <v>1.382</v>
       </c>
       <c r="E39" t="n">
-        <v>1.812</v>
+        <v>1.882</v>
       </c>
       <c r="F39" t="n">
-        <v>0.625</v>
+        <v>0.588</v>
       </c>
       <c r="G39" t="n">
-        <v>1.812</v>
+        <v>1.765</v>
       </c>
       <c r="H39" t="n">
-        <v>0.375</v>
+        <v>0.353</v>
       </c>
       <c r="I39" t="n">
-        <v>0.75</v>
+        <v>0.706</v>
       </c>
       <c r="J39" t="n">
-        <v>0.531</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>1.219</v>
+        <v>1.147</v>
       </c>
       <c r="L39" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.588</v>
       </c>
       <c r="M39" t="n">
-        <v>0.344</v>
+        <v>0.412</v>
       </c>
       <c r="N39" t="n">
-        <v>0.312</v>
+        <v>0.294</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.406</v>
+        <v>0.412</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.406</v>
+        <v>0.412</v>
       </c>
       <c r="R39" t="n">
-        <v>1.75</v>
+        <v>1.735</v>
       </c>
       <c r="S39" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.529</v>
       </c>
       <c r="T39" t="n">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="U39" t="n">
-        <v>0.969</v>
+        <v>0.912</v>
       </c>
       <c r="V39" t="n">
-        <v>0.781</v>
+        <v>0.794</v>
       </c>
       <c r="W39" t="n">
-        <v>0.25</v>
+        <v>0.294</v>
       </c>
       <c r="X39" t="n">
-        <v>0.156</v>
+        <v>0.176</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.469</v>
+        <v>1.559</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.156</v>
+        <v>2.206</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.681</v>
+        <v>0.707</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.125</v>
+        <v>0.118</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.219</v>
+        <v>0.206</v>
       </c>
       <c r="AD39" t="n">
         <v>0.571</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.188</v>
+        <v>0.176</v>
       </c>
       <c r="AG39" t="n">
         <v>0.333</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.219</v>
+        <v>0.206</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.75</v>
+        <v>0.765</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.292</v>
+        <v>0.269</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.406</v>
+        <v>0.382</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.062</v>
+        <v>1</v>
       </c>
       <c r="AM39" t="n">
         <v>0.382</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>4.361</v>
+        <v>4.369</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.612</v>
+        <v>0.621</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.608</v>
+        <v>0.617</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.103</v>
+        <v>1.117</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.103</v>
+        <v>0.097</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.308</v>
+        <v>1.357</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.143</v>
+        <v>0.14</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.045</v>
+        <v>0.046</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.098</v>
+        <v>0.09</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="40">
@@ -6405,153 +6405,153 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C40" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="D40" t="n">
-        <v>1.033</v>
+        <v>1.031</v>
       </c>
       <c r="E40" t="n">
-        <v>1.767</v>
+        <v>1.781</v>
       </c>
       <c r="F40" t="n">
-        <v>0.633</v>
+        <v>0.656</v>
       </c>
       <c r="G40" t="n">
-        <v>2.133</v>
+        <v>2.188</v>
       </c>
       <c r="H40" t="n">
-        <v>0.433</v>
+        <v>0.469</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="J40" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>1.733</v>
+        <v>1.75</v>
       </c>
       <c r="L40" t="n">
-        <v>0.533</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="N40" t="n">
-        <v>0.267</v>
+        <v>0.25</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.067</v>
+        <v>1.031</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.067</v>
+        <v>1.031</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>1.094</v>
       </c>
       <c r="S40" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="T40" t="n">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="U40" t="n">
-        <v>0.7</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="V40" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="W40" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="X40" t="n">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.033</v>
+        <v>1.094</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.4</v>
+        <v>1.469</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.738</v>
+        <v>0.745</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.233</v>
+        <v>0.219</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.412</v>
+        <v>0.389</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.2</v>
+        <v>0.188</v>
       </c>
       <c r="AF40" t="n">
         <v>0.5</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.3</v>
+        <v>0.281</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.767</v>
+        <v>0.75</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.391</v>
+        <v>0.375</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.333</v>
+        <v>0.375</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.367</v>
+        <v>1.438</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.244</v>
+        <v>0.261</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>5.275</v>
+        <v>5.33</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.509</v>
+        <v>0.508</v>
       </c>
       <c r="AQ40" t="n">
         <v>0.523</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.834</v>
+        <v>0.844</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.202</v>
+        <v>0.193</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.111</v>
+        <v>0.118</v>
       </c>
       <c r="AU40" t="n">
-        <v>0.875</v>
+        <v>0.909</v>
       </c>
       <c r="AV40" t="n">
         <v>0.202</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.05</v>
+        <v>0.052</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.162</v>
+        <v>0.163</v>
       </c>
       <c r="AY40" t="n">
         <v>0.034</v>
@@ -6564,156 +6564,156 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C41" t="n">
-        <v>5.643</v>
+        <v>5.933</v>
       </c>
       <c r="D41" t="n">
-        <v>0.714</v>
+        <v>0.767</v>
       </c>
       <c r="E41" t="n">
-        <v>1.429</v>
+        <v>1.533</v>
       </c>
       <c r="F41" t="n">
-        <v>1.214</v>
+        <v>1.267</v>
       </c>
       <c r="G41" t="n">
-        <v>3.179</v>
+        <v>3.233</v>
       </c>
       <c r="H41" t="n">
-        <v>0.571</v>
+        <v>0.6</v>
       </c>
       <c r="I41" t="n">
-        <v>0.75</v>
+        <v>0.833</v>
       </c>
       <c r="J41" t="n">
-        <v>0.571</v>
+        <v>0.633</v>
       </c>
       <c r="K41" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="L41" t="n">
-        <v>0.571</v>
+        <v>0.6</v>
       </c>
       <c r="M41" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="N41" t="n">
-        <v>0.571</v>
+        <v>0.6</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.286</v>
+        <v>0.3</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.286</v>
+        <v>0.3</v>
       </c>
       <c r="R41" t="n">
-        <v>1.143</v>
+        <v>1.2</v>
       </c>
       <c r="S41" t="n">
-        <v>0.643</v>
+        <v>0.767</v>
       </c>
       <c r="T41" t="n">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="U41" t="n">
-        <v>0.643</v>
+        <v>0.7</v>
       </c>
       <c r="V41" t="n">
-        <v>0.429</v>
+        <v>0.433</v>
       </c>
       <c r="W41" t="n">
-        <v>0.393</v>
+        <v>0.367</v>
       </c>
       <c r="X41" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.433</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="AD41" t="n">
         <v>0.143</v>
       </c>
-      <c r="Y41" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0.167</v>
-      </c>
       <c r="AE41" t="n">
-        <v>0.25</v>
+        <v>0.233</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.714</v>
+        <v>0.7</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.35</v>
+        <v>0.333</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.536</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.179</v>
+        <v>1.2</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.455</v>
+        <v>0.472</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.679</v>
+        <v>0.7</v>
       </c>
       <c r="AL41" t="n">
-        <v>2</v>
+        <v>2.033</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.339</v>
+        <v>0.344</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>5.223</v>
+        <v>5.433</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.55</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.571</v>
+        <v>0.578</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.08</v>
+        <v>1.092</v>
       </c>
       <c r="AS41" t="n">
         <v>0.055</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.124</v>
+        <v>0.126</v>
       </c>
       <c r="AU41" t="n">
-        <v>2</v>
+        <v>2.111</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.137</v>
+        <v>0.14</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.036</v>
+        <v>0.038</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.144</v>
+        <v>0.14</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.021</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="42">
@@ -6723,16 +6723,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C42" t="n">
-        <v>4.812</v>
+        <v>4.765</v>
       </c>
       <c r="D42" t="n">
-        <v>1.906</v>
+        <v>1.882</v>
       </c>
       <c r="E42" t="n">
-        <v>3.719</v>
+        <v>3.735</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -6744,79 +6744,79 @@
         <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>1.406</v>
+        <v>1.441</v>
       </c>
       <c r="J42" t="n">
-        <v>1.594</v>
+        <v>1.529</v>
       </c>
       <c r="K42" t="n">
-        <v>1.719</v>
+        <v>1.676</v>
       </c>
       <c r="L42" t="n">
-        <v>1.062</v>
+        <v>1.059</v>
       </c>
       <c r="M42" t="n">
-        <v>0.406</v>
+        <v>0.412</v>
       </c>
       <c r="N42" t="n">
-        <v>0.594</v>
+        <v>0.588</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0.75</v>
+        <v>0.794</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.75</v>
+        <v>0.794</v>
       </c>
       <c r="R42" t="n">
-        <v>1.281</v>
+        <v>1.324</v>
       </c>
       <c r="S42" t="n">
-        <v>1.281</v>
+        <v>1.265</v>
       </c>
       <c r="T42" t="n">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="U42" t="n">
-        <v>0.188</v>
+        <v>0.176</v>
       </c>
       <c r="V42" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="W42" t="n">
-        <v>0.188</v>
+        <v>0.235</v>
       </c>
       <c r="X42" t="n">
-        <v>0.125</v>
+        <v>0.147</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.219</v>
+        <v>2.206</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.062</v>
+        <v>3.088</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.724</v>
+        <v>0.714</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.438</v>
+        <v>0.441</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.312</v>
+        <v>1.324</v>
       </c>
       <c r="AD42" t="n">
         <v>0.333</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.25</v>
+        <v>0.235</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.75</v>
+        <v>0.765</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.333</v>
+        <v>0.308</v>
       </c>
       <c r="AH42" t="n">
         <v>0</v>
@@ -6838,41 +6838,41 @@
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>5.087</v>
+        <v>5.164</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.513</v>
+        <v>0.504</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.555</v>
+        <v>0.545</v>
       </c>
       <c r="AR42" t="n">
-        <v>0.946</v>
+        <v>0.923</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.147</v>
+        <v>0.154</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.269</v>
+        <v>0.268</v>
       </c>
       <c r="AU42" t="n">
-        <v>2.125</v>
+        <v>1.926</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.162</v>
+        <v>0.163</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.082</v>
+        <v>0.081</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.134</v>
+        <v>0.13</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.059</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="43">
@@ -7022,7 +7022,7 @@
         <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.406</v>
+        <v>0.404</v>
       </c>
       <c r="AW43" t="n">
         <v>0</v>
@@ -7340,7 +7340,7 @@
         <v>0</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.197</v>
+        <v>0.196</v>
       </c>
       <c r="AW45" t="n">
         <v>0</v>
@@ -7359,7 +7359,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -7386,10 +7386,10 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>1.844</v>
+        <v>1.794</v>
       </c>
       <c r="L46" t="n">
-        <v>1.25</v>
+        <v>1.265</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -7401,13 +7401,13 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.844</v>
+        <v>0.824</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.469</v>
+        <v>0.441</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -7518,118 +7518,118 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C47" t="n">
-        <v>83.53100000000001</v>
+        <v>84</v>
       </c>
       <c r="D47" t="n">
-        <v>21.188</v>
+        <v>21.265</v>
       </c>
       <c r="E47" t="n">
-        <v>38.844</v>
+        <v>39.088</v>
       </c>
       <c r="F47" t="n">
-        <v>7.688</v>
+        <v>7.765</v>
       </c>
       <c r="G47" t="n">
-        <v>24.094</v>
+        <v>24.029</v>
       </c>
       <c r="H47" t="n">
-        <v>18.094</v>
+        <v>18.176</v>
       </c>
       <c r="I47" t="n">
-        <v>23.812</v>
+        <v>24.059</v>
       </c>
       <c r="J47" t="n">
-        <v>17.062</v>
+        <v>17.147</v>
       </c>
       <c r="K47" t="n">
-        <v>25.375</v>
+        <v>25.059</v>
       </c>
       <c r="L47" t="n">
-        <v>10.438</v>
+        <v>10.559</v>
       </c>
       <c r="M47" t="n">
-        <v>6.656</v>
+        <v>6.676</v>
       </c>
       <c r="N47" t="n">
-        <v>6.281</v>
+        <v>6.206</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>13.562</v>
+        <v>13.706</v>
       </c>
       <c r="Q47" t="n">
-        <v>12.719</v>
+        <v>12.882</v>
       </c>
       <c r="R47" t="n">
-        <v>24.281</v>
+        <v>24.353</v>
       </c>
       <c r="S47" t="n">
-        <v>22.094</v>
+        <v>22.235</v>
       </c>
       <c r="T47" t="n">
-        <v>3002</v>
+        <v>3191</v>
       </c>
       <c r="U47" t="n">
-        <v>10.719</v>
+        <v>10.765</v>
       </c>
       <c r="V47" t="n">
-        <v>10.219</v>
+        <v>10.618</v>
       </c>
       <c r="W47" t="n">
         <v>5.5</v>
       </c>
       <c r="X47" t="n">
-        <v>3.406</v>
+        <v>3.441</v>
       </c>
       <c r="Y47" t="n">
-        <v>32.438</v>
+        <v>32.735</v>
       </c>
       <c r="Z47" t="n">
-        <v>43.312</v>
+        <v>44</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.749</v>
+        <v>0.744</v>
       </c>
       <c r="AB47" t="n">
-        <v>3.812</v>
+        <v>3.735</v>
       </c>
       <c r="AC47" t="n">
-        <v>10.094</v>
+        <v>9.912000000000001</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.378</v>
+        <v>0.377</v>
       </c>
       <c r="AE47" t="n">
-        <v>3.031</v>
+        <v>2.971</v>
       </c>
       <c r="AF47" t="n">
-        <v>9.25</v>
+        <v>9.234999999999999</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.328</v>
+        <v>0.322</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.188</v>
+        <v>2.206</v>
       </c>
       <c r="AI47" t="n">
-        <v>5.812</v>
+        <v>5.824</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.376</v>
+        <v>0.379</v>
       </c>
       <c r="AK47" t="n">
-        <v>5.5</v>
+        <v>5.559</v>
       </c>
       <c r="AL47" t="n">
-        <v>18.281</v>
+        <v>18.206</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.301</v>
+        <v>0.305</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
@@ -7637,34 +7637,34 @@
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>86.977</v>
+        <v>87.40900000000001</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.52</v>
+        <v>0.521</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.569</v>
+        <v>0.57</v>
       </c>
       <c r="AR47" t="n">
-        <v>0.96</v>
+        <v>0.961</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.156</v>
+        <v>0.157</v>
       </c>
       <c r="AT47" t="n">
-        <v>0.287</v>
+        <v>0.288</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.258</v>
+        <v>1.251</v>
       </c>
       <c r="AV47" t="n">
         <v>0.2</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.058</v>
+        <v>0.059</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.142</v>
+        <v>0.141</v>
       </c>
       <c r="AY47" t="n">
         <v>0</v>
@@ -7677,118 +7677,118 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C48" t="n">
-        <v>89.53100000000001</v>
+        <v>91.08799999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>18.781</v>
+        <v>19.176</v>
       </c>
       <c r="E48" t="n">
-        <v>34.469</v>
+        <v>34.824</v>
       </c>
       <c r="F48" t="n">
-        <v>10.688</v>
+        <v>10.941</v>
       </c>
       <c r="G48" t="n">
-        <v>29.781</v>
+        <v>30.029</v>
       </c>
       <c r="H48" t="n">
-        <v>19.906</v>
+        <v>19.912</v>
       </c>
       <c r="I48" t="n">
-        <v>25.594</v>
+        <v>25.529</v>
       </c>
       <c r="J48" t="n">
-        <v>17.25</v>
+        <v>17.235</v>
       </c>
       <c r="K48" t="n">
-        <v>25.312</v>
+        <v>25.324</v>
       </c>
       <c r="L48" t="n">
-        <v>10.281</v>
+        <v>10.559</v>
       </c>
       <c r="M48" t="n">
-        <v>7.188</v>
+        <v>7.324</v>
       </c>
       <c r="N48" t="n">
-        <v>6.281</v>
+        <v>6.235</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>12.062</v>
+        <v>12.029</v>
       </c>
       <c r="Q48" t="n">
-        <v>11.188</v>
+        <v>11.176</v>
       </c>
       <c r="R48" t="n">
-        <v>22.344</v>
+        <v>22.471</v>
       </c>
       <c r="S48" t="n">
-        <v>23.75</v>
+        <v>23.853</v>
       </c>
       <c r="T48" t="n">
-        <v>3351</v>
+        <v>3630</v>
       </c>
       <c r="U48" t="n">
-        <v>10.875</v>
+        <v>11.118</v>
       </c>
       <c r="V48" t="n">
-        <v>10.531</v>
+        <v>11.206</v>
       </c>
       <c r="W48" t="n">
-        <v>5.125</v>
+        <v>5.412</v>
       </c>
       <c r="X48" t="n">
-        <v>3.156</v>
+        <v>3.441</v>
       </c>
       <c r="Y48" t="n">
-        <v>31.656</v>
+        <v>32.029</v>
       </c>
       <c r="Z48" t="n">
-        <v>40.5</v>
+        <v>40.941</v>
       </c>
       <c r="AA48" t="n">
         <v>0.782</v>
       </c>
       <c r="AB48" t="n">
-        <v>3.5</v>
+        <v>3.412</v>
       </c>
       <c r="AC48" t="n">
-        <v>9.531000000000001</v>
+        <v>9.353</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.367</v>
+        <v>0.365</v>
       </c>
       <c r="AE48" t="n">
-        <v>3.531</v>
+        <v>3.647</v>
       </c>
       <c r="AF48" t="n">
-        <v>10.031</v>
+        <v>10.059</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.352</v>
+        <v>0.363</v>
       </c>
       <c r="AH48" t="n">
-        <v>3.094</v>
+        <v>3.118</v>
       </c>
       <c r="AI48" t="n">
-        <v>7.625</v>
+        <v>7.676</v>
       </c>
       <c r="AJ48" t="n">
         <v>0.406</v>
       </c>
       <c r="AK48" t="n">
-        <v>7.594</v>
+        <v>7.824</v>
       </c>
       <c r="AL48" t="n">
-        <v>22.156</v>
+        <v>22.353</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.343</v>
+        <v>0.35</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
@@ -7796,31 +7796,31 @@
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>87.574</v>
+        <v>88.11499999999999</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.542</v>
+        <v>0.549</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.593</v>
+        <v>0.599</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.022</v>
+        <v>1.034</v>
       </c>
       <c r="AS48" t="n">
-        <v>0.138</v>
+        <v>0.137</v>
       </c>
       <c r="AT48" t="n">
-        <v>0.31</v>
+        <v>0.307</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.43</v>
+        <v>1.433</v>
       </c>
       <c r="AV48" t="n">
-        <v>0.201</v>
+        <v>0.202</v>
       </c>
       <c r="AW48" t="n">
-        <v>0.058</v>
+        <v>0.059</v>
       </c>
       <c r="AX48" t="n">
         <v>0.142</v>
